--- a/export/Приложение_Б.xlsx
+++ b/export/Приложение_Б.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,70 +580,70 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>221.499</v>
+        <v>209.847</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>237.887</v>
+        <v>221.547</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>254.275</v>
+        <v>233.248</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>230.87</v>
+        <v>246.403</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>218.127</v>
+        <v>236.37</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>209.061</v>
+        <v>226.626</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>34.265</v>
+        <v>42.764</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>190.159</v>
+        <v>169.65</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>60.512</v>
+        <v>60.701</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>233.399</v>
+        <v>250.087</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>289.378</v>
+        <v>290.95</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>217.643</v>
+        <v>234.615</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>297.25</v>
+        <v>297.71</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>223.287</v>
+        <v>242</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>81.55800000000001</v>
+        <v>80.154</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>48.919</v>
+        <v>54.332</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>73.857</v>
+        <v>75.005</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>50.958</v>
+        <v>55.859</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>77.658</v>
+        <v>77.617</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>26.7</v>
+        <v>21.757</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>24.939</v>
+        <v>20.674</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.949</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="3">
@@ -651,70 +651,70 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>254.275</v>
+        <v>233.248</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>267.14</v>
+        <v>244.229</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>280.006</v>
+        <v>255.209</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>217.126</v>
+        <v>232.468</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>204.415</v>
+        <v>221.611</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>197.684</v>
+        <v>214.409</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>54.354</v>
+        <v>51.73</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>202.848</v>
+        <v>184.091</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>73.908</v>
+        <v>68.294</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>223.826</v>
+        <v>238.154</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>287.981</v>
+        <v>288.099</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>211.048</v>
+        <v>225.023</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>295.147</v>
+        <v>294.941</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>214.287</v>
+        <v>229.625</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>75.946</v>
+        <v>77.455</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>45.22</v>
+        <v>50.284</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>69.501</v>
+        <v>72.33199999999999</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>47.362</v>
+        <v>52.016</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>72.541</v>
+        <v>74.818</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>25.178</v>
+        <v>22.801</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>24.28</v>
+        <v>22.048</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.883</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="4">
@@ -722,70 +722,70 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>280.006</v>
+        <v>255.209</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>289.333</v>
+        <v>263.948</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>298.66</v>
+        <v>272.686</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>204.396</v>
+        <v>219.722</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>192.502</v>
+        <v>208.999</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>188.041</v>
+        <v>203.428</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>68.681</v>
+        <v>61.349</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>213.689</v>
+        <v>196.036</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>82.46299999999999</v>
+        <v>74.334</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>215.626</v>
+        <v>228.126</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>287.611</v>
+        <v>286.55</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>205.328</v>
+        <v>216.584</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>294</v>
+        <v>293.018</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>206.831</v>
+        <v>219.756</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>71.42700000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>42.014</v>
+        <v>46.833</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>66.321</v>
+        <v>69.92700000000001</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>44.045</v>
+        <v>48.578</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>68.548</v>
+        <v>71.999</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>24.502</v>
+        <v>23.421</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>24.307</v>
+        <v>23.094</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.827</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="5">
@@ -793,70 +793,70 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>298.66</v>
+        <v>272.686</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>305.223</v>
+        <v>279.2</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>311.786</v>
+        <v>285.713</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>193.294</v>
+        <v>207.85</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>182.355</v>
+        <v>197.618</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>180.106</v>
+        <v>193.763</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>81.669</v>
+        <v>71.905</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>218.818</v>
+        <v>202.535</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>91.08</v>
+        <v>81.35599999999999</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>209.839</v>
+        <v>219.936</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>284.841</v>
+        <v>282.972</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>201.826</v>
+        <v>210.15</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>290.599</v>
+        <v>288.989</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>201.79</v>
+        <v>211.968</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>67.095</v>
+        <v>70.917</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>39.807</v>
+        <v>44.296</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>63.174</v>
+        <v>67.224</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>41.694</v>
+        <v>45.991</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>64.64700000000001</v>
+        <v>68.79600000000001</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>22.953</v>
+        <v>22.806</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>23.368</v>
+        <v>22.928</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.771</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="6">
@@ -864,70 +864,70 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>311.786</v>
+        <v>285.713</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>316.599</v>
+        <v>290.676</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>321.412</v>
+        <v>295.639</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>184.287</v>
+        <v>197.45</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>173.955</v>
+        <v>187.573</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>173.404</v>
+        <v>185.123</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>90.40900000000001</v>
+        <v>79.355</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>222.788</v>
+        <v>207.756</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>97.18300000000001</v>
+        <v>86.449</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>205.269</v>
+        <v>212.8</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>282.657</v>
+        <v>279.904</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>198.78</v>
+        <v>204.314</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>288.045</v>
+        <v>285.606</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>197.638</v>
+        <v>205.084</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>63.868</v>
+        <v>68.105</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>37.983</v>
+        <v>42.077</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>60.732</v>
+        <v>64.968</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>39.776</v>
+        <v>43.736</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>61.663</v>
+        <v>66.151</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>21.887</v>
+        <v>22.415</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>22.749</v>
+        <v>22.891</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.725</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="7">
@@ -935,70 +935,70 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>321.412</v>
+        <v>295.639</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>325.055</v>
+        <v>299.493</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>328.699</v>
+        <v>303.346</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>176.786</v>
+        <v>188.215</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>166.813</v>
+        <v>178.567</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>167.617</v>
+        <v>177.297</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>96.59399999999999</v>
+        <v>84.741</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>225.921</v>
+        <v>212.013</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>101.659</v>
+        <v>90.19799999999999</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>201.454</v>
+        <v>206.412</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>280.832</v>
+        <v>277.193</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>196.036</v>
+        <v>198.922</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>286</v>
+        <v>282.671</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>194.047</v>
+        <v>198.844</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>61.348</v>
+        <v>65.761</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>36.441</v>
+        <v>40.106</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>58.763</v>
+        <v>63.036</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>38.18</v>
+        <v>41.747</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>59.278</v>
+        <v>63.9</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>21.098</v>
+        <v>22.153</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>22.322</v>
+        <v>22.93</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="8">
@@ -1006,70 +1006,70 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>328.699</v>
+        <v>303.346</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>331.529</v>
+        <v>306.388</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>334.359</v>
+        <v>309.43</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>170.392</v>
+        <v>179.906</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>160.602</v>
+        <v>170.386</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>162.524</v>
+        <v>170.126</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>101.132</v>
+        <v>88.709</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>228.442</v>
+        <v>215.534</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>105.032</v>
+        <v>92.989</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>198.145</v>
+        <v>200.588</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>279.247</v>
+        <v>274.748</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>193.509</v>
+        <v>193.881</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>284.289</v>
+        <v>280.064</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>190.84</v>
+        <v>193.096</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>59.31</v>
+        <v>63.753</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>35.108</v>
+        <v>38.327</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>57.127</v>
+        <v>61.34</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>36.824</v>
+        <v>39.969</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>57.304</v>
+        <v>61.932</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>20.48</v>
+        <v>21.963</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>22.019</v>
+        <v>23.012</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.655</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="9">
@@ -1077,70 +1077,70 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>334.359</v>
+        <v>309.43</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>336.604</v>
+        <v>311.866</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>338.848</v>
+        <v>314.301</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>164.832</v>
+        <v>172.344</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>155.097</v>
+        <v>162.869</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>157.97</v>
+        <v>163.489</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>104.554</v>
+        <v>91.673</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>230.51</v>
+        <v>218.483</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>107.628</v>
+        <v>95.086</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>195.195</v>
+        <v>195.208</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>277.831</v>
+        <v>272.509</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>191.15</v>
+        <v>189.13</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>282.808</v>
+        <v>277.706</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>187.912</v>
+        <v>187.741</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>57.613</v>
+        <v>61.991</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>33.934</v>
+        <v>36.703</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>55.733</v>
+        <v>59.818</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>35.651</v>
+        <v>38.36</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>55.626</v>
+        <v>60.172</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>19.975</v>
+        <v>21.812</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>21.798</v>
+        <v>23.115</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.627</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="10">
@@ -1148,70 +1148,70 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>338.848</v>
+        <v>314.301</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>338.848</v>
+        <v>316.275</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>338.848</v>
+        <v>318.248</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>156.084</v>
+        <v>165.387</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>148.148</v>
+        <v>155.895</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>152.849</v>
+        <v>157.295</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>107.189</v>
+        <v>93.913</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>231.659</v>
+        <v>220.98</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>107.189</v>
+        <v>96.67100000000001</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>189.345</v>
+        <v>190.191</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>274.98</v>
+        <v>270.436</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>186.687</v>
+        <v>184.627</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>279.335</v>
+        <v>275.543</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>182.858</v>
+        <v>182.714</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>55.521</v>
+        <v>60.41</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>32.599</v>
+        <v>35.202</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>54.959</v>
+        <v>58.426</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>33.971</v>
+        <v>36.886</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>54.113</v>
+        <v>58.564</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>20.143</v>
+        <v>21.678</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>22.36</v>
+        <v>23.224</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.597</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="11">
@@ -1219,70 +1219,70 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>338.848</v>
+        <v>318.248</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>338.848</v>
+        <v>319.865</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>338.848</v>
+        <v>321.481</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>151.225</v>
+        <v>158.93</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>142.921</v>
+        <v>149.371</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>148.237</v>
+        <v>151.471</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>106.779</v>
+        <v>95.621</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>232.069</v>
+        <v>223.115</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>106.779</v>
+        <v>97.876</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>185.123</v>
+        <v>185.478</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>272.548</v>
+        <v>268.499</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>182.69</v>
+        <v>180.342</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>276.993</v>
+        <v>273.536</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>178.404</v>
+        <v>177.967</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>54.774</v>
+        <v>58.967</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>31.627</v>
+        <v>33.802</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>54.234</v>
+        <v>57.131</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>33.09</v>
+        <v>35.522</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>53.236</v>
+        <v>57.068</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>20.146</v>
+        <v>21.546</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>22.607</v>
+        <v>23.329</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.573</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="12">
@@ -1290,70 +1290,70 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>338.848</v>
+        <v>321.481</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>338.848</v>
+        <v>321.481</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>338.848</v>
+        <v>321.481</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>145.868</v>
+        <v>150.081</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>137.137</v>
+        <v>141.75</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>143.106</v>
+        <v>145.203</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>102.769</v>
+        <v>96.931</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>222.525</v>
+        <v>224.55</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>102.769</v>
+        <v>96.931</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>178.435</v>
+        <v>178.662</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>261.388</v>
+        <v>265.548</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>176.184</v>
+        <v>174.584</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>277.508</v>
+        <v>270.087</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>179.827</v>
+        <v>171.723</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>54.834</v>
+        <v>57.143</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>31.645</v>
+        <v>32.263</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>54.317</v>
+        <v>56.275</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>31.711</v>
+        <v>33.757</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>49.695</v>
+        <v>55.635</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>17.984</v>
+        <v>21.878</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>22.672</v>
+        <v>24.012</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1361,70 +1361,141 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>338.848</v>
+        <v>321.481</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>338.848</v>
+        <v>321.481</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>338.848</v>
+        <v>321.481</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>141.131</v>
+        <v>142.993</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>131.979</v>
+        <v>134.303</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>131.979</v>
+        <v>138.4</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>95.431</v>
+        <v>92.877</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>209.532</v>
+        <v>215.745</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>95.431</v>
+        <v>92.877</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>170.367</v>
+        <v>170.508</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>247.633</v>
+        <v>254.132</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>162.866</v>
+        <v>166.675</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>281.371</v>
+        <v>269.642</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>184.772</v>
+        <v>170.931</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>55.934</v>
+        <v>56.995</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>32.206</v>
+        <v>31.903</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>54.13</v>
+        <v>56.135</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>30.105</v>
+        <v>32.026</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>45.584</v>
+        <v>51.787</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>15.479</v>
+        <v>19.761</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>21.924</v>
+        <v>24.233</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.551</v>
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>321.481</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>321.481</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>321.481</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>136.395</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>127.342</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>127.342</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>85.76600000000001</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>203.567</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>85.76600000000001</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>161.119</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>240.116</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>153.531</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>272.333</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>173.55</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>57.838</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>32.028</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>56.04</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>30.055</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>47.202</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>17.146</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>24.011</v>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>0.534</v>
       </c>
     </row>
   </sheetData>
@@ -1438,7 +1509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1588,70 +1659,70 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>304.421</v>
+        <v>288.407</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>310.542</v>
+        <v>292.75</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>316.969</v>
+        <v>297.259</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>166.124</v>
+        <v>196.344</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>160.124</v>
+        <v>190.344</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>160.623</v>
+        <v>185.419</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>105.037</v>
+        <v>104.749</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>211.932</v>
+        <v>192.51</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>105.037</v>
+        <v>104.749</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>196.545</v>
+        <v>222.538</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>265.622</v>
+        <v>270.723</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>191.918</v>
+        <v>212.962</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>269.281</v>
+        <v>274.975</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>191.5</v>
+        <v>217.263</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>57.696</v>
+        <v>61.92</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>37.073</v>
+        <v>44.676</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>56.818</v>
+        <v>60.537</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>38.091</v>
+        <v>45.565</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>56.736</v>
+        <v>61.175</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>18.645</v>
+        <v>15.611</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>19.745</v>
+        <v>15.861</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.846</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="3">
@@ -1659,70 +1730,70 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>316.969</v>
+        <v>297.259</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>322.216</v>
+        <v>301.636</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>327.632</v>
+        <v>306.148</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>160.623</v>
+        <v>185.419</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>154.26</v>
+        <v>179.086</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>156.873</v>
+        <v>177.971</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>107.329</v>
+        <v>103.632</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>220.303</v>
+        <v>202.516</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>107.329</v>
+        <v>103.632</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>193.182</v>
+        <v>212.414</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>268.941</v>
+        <v>270.341</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>190.076</v>
+        <v>205.945</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>272.641</v>
+        <v>274.578</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>187.925</v>
+        <v>206.909</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>56.249</v>
+        <v>60.799</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>35</v>
+        <v>41.487</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>55.621</v>
+        <v>59.788</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>36.096</v>
+        <v>42.477</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>55.171</v>
+        <v>59.943</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>19.075</v>
+        <v>17.467</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>20.621</v>
+        <v>18.301</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.806</v>
+        <v>0.824</v>
       </c>
     </row>
     <row r="4">
@@ -1730,70 +1801,70 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>327.632</v>
+        <v>306.148</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>331.66</v>
+        <v>309.83</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>335.768</v>
+        <v>313.591</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>156.873</v>
+        <v>177.971</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>150.146</v>
+        <v>171.304</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>153.585</v>
+        <v>171.441</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>108.407</v>
+        <v>102.875</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>227.361</v>
+        <v>210.716</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>108.407</v>
+        <v>102.875</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>190.686</v>
+        <v>205.565</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>272.464</v>
+        <v>271.563</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>187.991</v>
+        <v>199.938</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>276.229</v>
+        <v>275.817</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>185.191</v>
+        <v>199.821</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>55.354</v>
+        <v>59.97</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>33.44</v>
+        <v>39.11</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>54.784</v>
+        <v>59.034</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>34.605</v>
+        <v>40.184</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>54.17</v>
+        <v>59.013</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>19.566</v>
+        <v>18.829</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>21.344</v>
+        <v>19.924</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.771</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="5">
@@ -1801,70 +1872,70 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>335.768</v>
+        <v>313.591</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>338.706</v>
+        <v>316.444</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>341.682</v>
+        <v>319.338</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>153.585</v>
+        <v>171.441</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>146.494</v>
+        <v>164.441</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>150.566</v>
+        <v>165.444</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>111.699</v>
+        <v>104.644</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>229.983</v>
+        <v>214.694</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>111.699</v>
+        <v>104.644</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>189.908</v>
+        <v>200.854</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>272.677</v>
+        <v>270.433</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>187.475</v>
+        <v>195.761</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>276.551</v>
+        <v>274.746</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>184.221</v>
+        <v>194.914</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>53.972</v>
+        <v>58.601</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>32.496</v>
+        <v>37.45</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>53.43</v>
+        <v>57.686</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>33.735</v>
+        <v>38.609</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>52.675</v>
+        <v>57.529</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>18.94</v>
+        <v>18.92</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>20.933</v>
+        <v>20.237</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.729</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="6">
@@ -1872,70 +1943,70 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>341.682</v>
+        <v>319.338</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>343.888</v>
+        <v>321.57</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>346.113</v>
+        <v>323.824</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>150.566</v>
+        <v>165.444</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>143.111</v>
+        <v>158.111</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>147.731</v>
+        <v>159.815</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>114.067</v>
+        <v>105.883</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>232.046</v>
+        <v>217.94</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>114.067</v>
+        <v>105.883</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>188.895</v>
+        <v>196.426</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>272.628</v>
+        <v>269.253</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>186.643</v>
+        <v>191.709</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>276.614</v>
+        <v>273.624</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>183.008</v>
+        <v>190.29</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>52.853</v>
+        <v>57.381</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>31.664</v>
+        <v>35.96</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>52.328</v>
+        <v>56.474</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>32.978</v>
+        <v>37.203</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>51.443</v>
+        <v>56.191</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>18.465</v>
+        <v>18.988</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>20.664</v>
+        <v>20.514</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.694</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="7">
@@ -1943,70 +2014,70 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>346.113</v>
+        <v>323.824</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>347.81</v>
+        <v>325.59</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>349.518</v>
+        <v>327.369</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>147.731</v>
+        <v>159.815</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>139.913</v>
+        <v>152.148</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>145.036</v>
+        <v>154.463</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>115.803</v>
+        <v>106.72</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>233.715</v>
+        <v>220.649</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>115.803</v>
+        <v>106.72</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>187.709</v>
+        <v>192.172</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>272.394</v>
+        <v>268.021</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>185.596</v>
+        <v>187.744</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>276.491</v>
+        <v>272.446</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>181.62</v>
+        <v>185.845</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>51.908</v>
+        <v>56.266</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>30.907</v>
+        <v>34.588</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>51.395</v>
+        <v>55.359</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>32.297</v>
+        <v>35.916</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>50.386</v>
+        <v>54.953</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>18.089</v>
+        <v>19.038</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>20.488</v>
+        <v>20.771</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.662</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="8">
@@ -2014,70 +2085,70 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>349.518</v>
+        <v>327.369</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>350.852</v>
+        <v>328.782</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>352.192</v>
+        <v>330.203</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>145.036</v>
+        <v>154.463</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>136.854</v>
+        <v>146.463</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>142.452</v>
+        <v>149.329</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>117.096</v>
+        <v>107.258</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>235.097</v>
+        <v>222.945</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>117.096</v>
+        <v>107.258</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>186.405</v>
+        <v>188.05</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>272.029</v>
+        <v>266.75</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>184.401</v>
+        <v>183.858</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>276.235</v>
+        <v>271.225</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>180.113</v>
+        <v>181.537</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>51.084</v>
+        <v>55.224</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>30.205</v>
+        <v>33.303</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>50.58</v>
+        <v>54.312</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>31.671</v>
+        <v>34.715</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>49.449</v>
+        <v>53.784</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>17.778</v>
+        <v>19.068</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>20.375</v>
+        <v>21.009</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.635</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="9">
@@ -2085,70 +2156,70 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>352.192</v>
+        <v>330.203</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>353.259</v>
+        <v>331.347</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>354.331</v>
+        <v>332.496</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>142.452</v>
+        <v>149.329</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>133.906</v>
+        <v>140.996</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>139.958</v>
+        <v>144.377</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>118.069</v>
+        <v>107.579</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>236.261</v>
+        <v>224.917</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>118.069</v>
+        <v>107.579</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>185.021</v>
+        <v>184.045</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>271.57</v>
+        <v>265.457</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>183.108</v>
+        <v>180.05</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>275.884</v>
+        <v>269.975</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>178.525</v>
+        <v>177.35</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>50.347</v>
+        <v>54.231</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>29.543</v>
+        <v>32.083</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>49.849</v>
+        <v>53.309</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>31.088</v>
+        <v>33.581</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>48.596</v>
+        <v>52.657</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>17.509</v>
+        <v>19.075</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>20.306</v>
+        <v>21.226</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.61</v>
+        <v>0.617</v>
       </c>
     </row>
     <row r="10">
@@ -2156,70 +2227,70 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>354.331</v>
+        <v>332.496</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>353.492</v>
+        <v>333.43</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>352.655</v>
+        <v>334.368</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>139.958</v>
+        <v>144.377</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>131.049</v>
+        <v>135.711</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>136.341</v>
+        <v>139.578</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>116.529</v>
+        <v>107.742</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>236.126</v>
+        <v>226.626</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>116.529</v>
+        <v>107.742</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>182.119</v>
+        <v>180.147</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>270.055</v>
+        <v>264.153</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>179.354</v>
+        <v>176.324</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>274.488</v>
+        <v>268.708</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>175.365</v>
+        <v>173.279</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>50.219</v>
+        <v>53.268</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>29.03</v>
+        <v>30.914</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>49.48</v>
+        <v>52.335</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>30.656</v>
+        <v>32.5</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>48.356</v>
+        <v>51.554</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>17.7</v>
+        <v>19.054</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>20.45</v>
+        <v>21.421</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.586</v>
+        <v>0.593</v>
       </c>
     </row>
     <row r="11">
@@ -2227,70 +2298,70 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>352.655</v>
+        <v>334.368</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>351.953</v>
+        <v>335.138</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>351.252</v>
+        <v>335.91</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>136.341</v>
+        <v>139.578</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>127.068</v>
+        <v>130.578</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>133.019</v>
+        <v>134.91</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>115.193</v>
+        <v>107.791</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>236.059</v>
+        <v>228.119</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>115.193</v>
+        <v>107.791</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>178.489</v>
+        <v>176.354</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>268.086</v>
+        <v>262.848</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>175.964</v>
+        <v>172.683</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>272.604</v>
+        <v>267.433</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>171.51</v>
+        <v>169.32</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>49.806</v>
+        <v>52.322</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>28.293</v>
+        <v>29.787</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>49.108</v>
+        <v>51.376</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>30.009</v>
+        <v>31.461</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>47.806</v>
+        <v>50.461</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>17.797</v>
+        <v>19</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>20.815</v>
+        <v>21.589</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.571</v>
       </c>
     </row>
     <row r="12">
@@ -2298,70 +2369,70 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>351.252</v>
+        <v>335.91</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>350.693</v>
+        <v>335.284</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>350.135</v>
+        <v>334.66</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>133.019</v>
+        <v>134.91</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>123.383</v>
+        <v>125.577</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>129.985</v>
+        <v>129.461</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>110.117</v>
+        <v>106.033</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>226.012</v>
+        <v>228.626</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>110.117</v>
+        <v>106.033</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>172.684</v>
+        <v>171.592</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>257.497</v>
+        <v>260.844</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>170.358</v>
+        <v>167.342</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>274.413</v>
+        <v>265.463</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>175.013</v>
+        <v>164.355</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>50.381</v>
+        <v>51.834</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>28.631</v>
+        <v>28.778</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>49.73</v>
+        <v>50.681</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>28.995</v>
+        <v>30.544</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>44.829</v>
+        <v>49.823</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>15.833</v>
+        <v>19.279</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>21.1</v>
+        <v>21.903</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.551</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="13">
@@ -2369,70 +2440,141 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>350.135</v>
+        <v>334.66</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>349.91</v>
+        <v>334.176</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>349.685</v>
+        <v>333.692</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>129.985</v>
+        <v>129.461</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>119.985</v>
+        <v>119.795</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>119.985</v>
+        <v>124.37</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>102.076</v>
+        <v>100.987</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>212.641</v>
+        <v>219.358</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>102.076</v>
+        <v>100.987</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>165.274</v>
+        <v>164.19</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>244.157</v>
+        <v>249.937</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>157.53</v>
+        <v>160.207</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>279.654</v>
+        <v>266.293</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>182.147</v>
+        <v>165.599</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>51.858</v>
+        <v>52.044</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>29.434</v>
+        <v>28.64</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>49.611</v>
+        <v>50.924</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>27.698</v>
+        <v>29.089</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>41.203</v>
+        <v>46.336</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>13.505</v>
+        <v>17.247</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>20.177</v>
+        <v>22.284</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.548</v>
+        <v>0.536</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>333.692</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>333.498</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>333.305</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>124.37</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>114.37</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>114.37</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>93.176</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>206.798</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>93.176</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>155.402</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>236.318</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>147.52</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>270.425</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>170.542</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>53.16</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>28.945</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>50.831</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>27.381</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>42.116</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>14.735</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>21.886</v>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>0.531</v>
       </c>
     </row>
   </sheetData>
@@ -2446,7 +2588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2596,70 +2738,70 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>98.44</v>
+        <v>146.873</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>87.937</v>
+        <v>138.75</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>88.843</v>
+        <v>131.914</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>138.692</v>
+        <v>137.577</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>230.473</v>
+        <v>212.168</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>138.692</v>
+        <v>137.577</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>170.076</v>
+        <v>201.244</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>246.68</v>
+        <v>253.509</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>164.707</v>
+        <v>190.601</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>250.616</v>
+        <v>258.045</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>164.22</v>
+        <v>195.395</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>35.366</v>
+        <v>46.872</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>20.884</v>
+        <v>33.183</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>32.643</v>
+        <v>43.796</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>23.128</v>
+        <v>34.693</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>32.377</v>
+        <v>45.243</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>9.247999999999999</v>
+        <v>10.55</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>11.758</v>
+        <v>10.613</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.78</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="3">
@@ -2667,70 +2809,70 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>106.443</v>
+        <v>141.714</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>96.57299999999999</v>
+        <v>133.321</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>100.694</v>
+        <v>131.819</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>134.451</v>
+        <v>131.593</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>234.714</v>
+        <v>218.151</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>134.451</v>
+        <v>131.593</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>171.485</v>
+        <v>193.39</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>253.805</v>
+        <v>255.664</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>167.977</v>
+        <v>186.261</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>257.722</v>
+        <v>260.14</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>165.539</v>
+        <v>187.327</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>38.368</v>
+        <v>47.121</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>22.365</v>
+        <v>31.431</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>36.831</v>
+        <v>45.049</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>24.394</v>
+        <v>33.008</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>35.689</v>
+        <v>45.374</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>11.294</v>
+        <v>12.365</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>14.466</v>
+        <v>13.618</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.757</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="4">
@@ -2738,70 +2880,70 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>113.305</v>
+        <v>140.295</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>103.791</v>
+        <v>131.736</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>108.707</v>
+        <v>131.914</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>130.486</v>
+        <v>126.526</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>238.679</v>
+        <v>223.219</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>130.486</v>
+        <v>126.526</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>172.814</v>
+        <v>188.922</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>260.269</v>
+        <v>259.193</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>169.835</v>
+        <v>182.784</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>264.208</v>
+        <v>263.647</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>166.731</v>
+        <v>182.656</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>40.969</v>
+        <v>47.954</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>23.502</v>
+        <v>30.548</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>39.798</v>
+        <v>46.194</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>25.394</v>
+        <v>32.15</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>38.499</v>
+        <v>46.156</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>13.105</v>
+        <v>14.006</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>16.295</v>
+        <v>15.647</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.734</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="5">
@@ -2809,70 +2951,70 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>117.56</v>
+        <v>138.635</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>108.132</v>
+        <v>129.879</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>113.587</v>
+        <v>131.147</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>129.843</v>
+        <v>124.632</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>239.321</v>
+        <v>225.113</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>129.843</v>
+        <v>124.632</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>175.156</v>
+        <v>186.421</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>262.616</v>
+        <v>259.893</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>172.515</v>
+        <v>180.921</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>266.637</v>
+        <v>264.378</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>168.973</v>
+        <v>180.004</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>42.158</v>
+        <v>48.045</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>24.315</v>
+        <v>29.983</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>41.179</v>
+        <v>46.459</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>26.161</v>
+        <v>31.627</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>39.787</v>
+        <v>46.181</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>13.626</v>
+        <v>14.554</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>16.865</v>
+        <v>16.476</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.701</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="6">
@@ -2880,70 +3022,70 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>120.107</v>
+        <v>136.536</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>110.619</v>
+        <v>127.551</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>116.535</v>
+        <v>129.658</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>129.276</v>
+        <v>122.996</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>239.889</v>
+        <v>226.748</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>129.276</v>
+        <v>122.996</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>176.46</v>
+        <v>183.767</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>264.165</v>
+        <v>260.162</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>174.048</v>
+        <v>178.716</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>268.277</v>
+        <v>264.683</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>170.144</v>
+        <v>177.193</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>42.894</v>
+        <v>47.986</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>24.756</v>
+        <v>29.359</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>42.033</v>
+        <v>46.51</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>26.596</v>
+        <v>31.054</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>40.553</v>
+        <v>46.042</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>13.957</v>
+        <v>14.987</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>17.277</v>
+        <v>17.152</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.671</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2951,70 +3093,70 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>121.51</v>
+        <v>134.035</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>111.874</v>
+        <v>124.794</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>118.219</v>
+        <v>127.605</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>128.764</v>
+        <v>121.552</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>240.401</v>
+        <v>228.192</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>128.764</v>
+        <v>121.552</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>177.045</v>
+        <v>180.943</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>265.158</v>
+        <v>260.087</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>174.802</v>
+        <v>176.233</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>269.365</v>
+        <v>264.645</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>170.575</v>
+        <v>174.208</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>43.34</v>
+        <v>47.796</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>24.956</v>
+        <v>28.673</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>42.555</v>
+        <v>46.392</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>26.814</v>
+        <v>30.429</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>40.985</v>
+        <v>45.754</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>14.171</v>
+        <v>15.325</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>17.6</v>
+        <v>17.718</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.644</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="8">
@@ -3022,70 +3164,70 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>122.122</v>
+        <v>131.206</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>112.283</v>
+        <v>121.687</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>119.041</v>
+        <v>125.123</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>128.294</v>
+        <v>120.261</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>240.87</v>
+        <v>229.484</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>128.294</v>
+        <v>120.261</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>177.125</v>
+        <v>177.983</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>265.755</v>
+        <v>259.751</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>175.015</v>
+        <v>173.547</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>270.06</v>
+        <v>264.344</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>170.49</v>
+        <v>171.086</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>43.588</v>
+        <v>47.492</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>24.993</v>
+        <v>27.935</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>42.858</v>
+        <v>46.135</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>26.885</v>
+        <v>29.759</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>41.192</v>
+        <v>45.338</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>14.307</v>
+        <v>15.579</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>17.865</v>
+        <v>18.2</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.62</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="9">
@@ -3093,70 +3235,70 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>122.173</v>
+        <v>128.122</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>112.093</v>
+        <v>118.304</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>119.257</v>
+        <v>122.314</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>127.861</v>
+        <v>119.097</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>241.304</v>
+        <v>230.648</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>127.861</v>
+        <v>119.097</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>176.847</v>
+        <v>174.927</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>266.068</v>
+        <v>259.218</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>174.844</v>
+        <v>170.719</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>270.47</v>
+        <v>263.844</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>170.039</v>
+        <v>167.869</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>43.697</v>
+        <v>47.091</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>24.916</v>
+        <v>27.154</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>43.006</v>
+        <v>45.764</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>26.853</v>
+        <v>29.052</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>41.24</v>
+        <v>44.809</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>14.387</v>
+        <v>15.757</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>18.09</v>
+        <v>18.609</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.598</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="10">
@@ -3164,70 +3306,70 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>369.165</v>
+        <v>349.745</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>367.553</v>
+        <v>349.745</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>365.942</v>
+        <v>349.745</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>116.747</v>
+        <v>124.84</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>108.669</v>
+        <v>114.706</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>117.537</v>
+        <v>119.257</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>127.458</v>
+        <v>118.044</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>241.151</v>
+        <v>231.701</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>125.343</v>
+        <v>118.044</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>172.845</v>
+        <v>171.812</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>264.505</v>
+        <v>258.54</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>171.831</v>
+        <v>167.799</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>268.425</v>
+        <v>263.193</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>166.693</v>
+        <v>164.596</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>42.489</v>
+        <v>46.603</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>24.258</v>
+        <v>26.338</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>43.159</v>
+        <v>45.293</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>25.781</v>
+        <v>28.316</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>40.686</v>
+        <v>44.179</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>14.905</v>
+        <v>15.863</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>18.901</v>
+        <v>18.955</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.573</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="11">
@@ -3235,70 +3377,70 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>365.942</v>
+        <v>349.745</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>364.587</v>
+        <v>349.745</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>363.233</v>
+        <v>349.745</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>115.417</v>
+        <v>121.405</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>106.646</v>
+        <v>110.94</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>115.819</v>
+        <v>116.008</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>124.964</v>
+        <v>117.088</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>240.516</v>
+        <v>232.657</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>123.177</v>
+        <v>117.088</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>170.109</v>
+        <v>168.667</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>263.1</v>
+        <v>257.754</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>169.076</v>
+        <v>164.825</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>267.192</v>
+        <v>262.428</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>163.606</v>
+        <v>161.299</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>42.726</v>
+        <v>46.037</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>23.913</v>
+        <v>25.494</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>43.237</v>
+        <v>44.735</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>25.592</v>
+        <v>27.556</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>40.681</v>
+        <v>43.456</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>15.089</v>
+        <v>15.899</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>19.324</v>
+        <v>19.241</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.552</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -3306,70 +3448,70 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>363.233</v>
+        <v>349.745</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>362.151</v>
+        <v>348.542</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>361.069</v>
+        <v>347.339</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>115.709</v>
+        <v>114.187</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>106.204</v>
+        <v>105.011</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>115.381</v>
+        <v>111.519</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>118.494</v>
+        <v>116.22</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>229.857</v>
+        <v>233.126</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>117.12</v>
+        <v>114.61</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>165.618</v>
+        <v>162.928</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>253.207</v>
+        <v>255.686</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>164.408</v>
+        <v>159.913</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>270.713</v>
+        <v>259.947</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>169.649</v>
+        <v>156.039</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>44.319</v>
+        <v>44.495</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>24.799</v>
+        <v>24.249</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>44.571</v>
+        <v>44.217</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>25.304</v>
+        <v>26.057</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>38.757</v>
+        <v>42.298</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>13.453</v>
+        <v>16.24</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>19.772</v>
+        <v>19.968</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.543</v>
+        <v>0.537</v>
       </c>
     </row>
     <row r="13">
@@ -3377,70 +3519,141 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>361.069</v>
+        <v>347.339</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>360.632</v>
+        <v>346.406</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>360.196</v>
+        <v>345.472</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>116.701</v>
+        <v>111.703</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>106.052</v>
+        <v>101.816</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>106.651</v>
+        <v>108.541</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>108.941</v>
+        <v>109.862</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>215.889</v>
+        <v>223.288</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>108.419</v>
+        <v>108.659</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>159.648</v>
+        <v>156.676</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>240.531</v>
+        <v>245.406</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>152.082</v>
+        <v>153.584</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>277.826</v>
+        <v>262.436</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>179.437</v>
+        <v>159.764</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46.97</v>
+        <v>45.476</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>26.162</v>
+        <v>24.512</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>44.529</v>
+        <v>44.969</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>24.838</v>
+        <v>25.191</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>36.23</v>
+        <v>39.59</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>11.392</v>
+        <v>14.399</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>18.367</v>
+        <v>20.457</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.544</v>
+        <v>0.528</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>345.472</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>345.098</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>344.723</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>110.104</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>99.19799999999999</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>99.724</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>100.652</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>210.164</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>100.196</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>149.177</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>232.399</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>141.366</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>268.44</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>167.474</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>47.568</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>25.268</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>44.865</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>24.215</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>36.322</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>12.107</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>19.597</v>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>0.526</v>
       </c>
     </row>
   </sheetData>

--- a/export/Приложение_Б.xlsx
+++ b/export/Приложение_Б.xlsx
@@ -580,70 +580,70 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>209.847</v>
+        <v>173.713</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>221.547</v>
+        <v>193.116</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>233.248</v>
+        <v>212.519</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>246.403</v>
+        <v>225.437</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>236.37</v>
+        <v>213.126</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>226.626</v>
+        <v>204.536</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>42.764</v>
+        <v>-2.951</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>169.65</v>
+        <v>177.342</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>60.701</v>
+        <v>32.851</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>250.087</v>
+        <v>225.456</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>290.95</v>
+        <v>277.26</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>234.615</v>
+        <v>207.157</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>297.71</v>
+        <v>286.412</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>242</v>
+        <v>213.709</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>80.154</v>
+        <v>90.75</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>54.332</v>
+        <v>50.236</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>75.005</v>
+        <v>80.876</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>55.859</v>
+        <v>51.916</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>77.617</v>
+        <v>85.767</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>21.757</v>
+        <v>33.851</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>20.674</v>
+        <v>30.639</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.95</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="3">
@@ -651,70 +651,70 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>233.248</v>
+        <v>212.519</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>244.229</v>
+        <v>227.269</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>255.209</v>
+        <v>242.02</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>232.468</v>
+        <v>212.573</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>221.611</v>
+        <v>200.162</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>214.409</v>
+        <v>193.627</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>51.73</v>
+        <v>26.176</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>184.091</v>
+        <v>188.521</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>68.294</v>
+        <v>50.688</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>238.154</v>
+        <v>214.178</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>288.099</v>
+        <v>274.963</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>225.023</v>
+        <v>200.152</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>294.941</v>
+        <v>282.685</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>229.625</v>
+        <v>203.878</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>77.455</v>
+        <v>82.98</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>50.284</v>
+        <v>46.716</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>72.33199999999999</v>
+        <v>75.33</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>52.016</v>
+        <v>48.762</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>74.818</v>
+        <v>79.044</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>22.801</v>
+        <v>30.282</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>22.048</v>
+        <v>28.615</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.894</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="4">
@@ -722,70 +722,70 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>255.209</v>
+        <v>242.02</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>263.948</v>
+        <v>252.722</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>272.686</v>
+        <v>263.424</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>219.722</v>
+        <v>200.49</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>208.999</v>
+        <v>188.726</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>203.428</v>
+        <v>184.218</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>61.349</v>
+        <v>45.188</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>196.036</v>
+        <v>198.973</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>74.334</v>
+        <v>62.05</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>228.126</v>
+        <v>205.519</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>286.55</v>
+        <v>274.24</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>216.584</v>
+        <v>194.387</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>293.018</v>
+        <v>280.961</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>219.756</v>
+        <v>196.231</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>77.29900000000001</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>46.833</v>
+        <v>43.486</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>69.92700000000001</v>
+        <v>71.38500000000001</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>48.578</v>
+        <v>45.527</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>71.999</v>
+        <v>74.10299999999999</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>23.421</v>
+        <v>28.576</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>23.094</v>
+        <v>27.899</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.843</v>
+        <v>0.793</v>
       </c>
     </row>
     <row r="5">
@@ -793,70 +793,70 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>272.686</v>
+        <v>263.424</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>279.2</v>
+        <v>270.995</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>285.713</v>
+        <v>278.567</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>207.85</v>
+        <v>189.706</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>197.618</v>
+        <v>178.829</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>193.763</v>
+        <v>176.403</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>71.905</v>
+        <v>61.267</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>202.535</v>
+        <v>203.975</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>81.35599999999999</v>
+        <v>72.66800000000001</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>219.936</v>
+        <v>199.353</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>282.972</v>
+        <v>271.267</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>210.15</v>
+        <v>190.784</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>288.989</v>
+        <v>277.229</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>211.968</v>
+        <v>190.976</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>70.917</v>
+        <v>72.102</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>44.296</v>
+        <v>41.242</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>67.224</v>
+        <v>67.611</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>45.991</v>
+        <v>43.18</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>68.79600000000001</v>
+        <v>69.455</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>22.806</v>
+        <v>26.275</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>22.928</v>
+        <v>26.369</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.788</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="6">
@@ -864,70 +864,70 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>285.713</v>
+        <v>278.567</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>290.676</v>
+        <v>284.161</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>295.639</v>
+        <v>289.755</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>197.45</v>
+        <v>180.852</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>187.573</v>
+        <v>170.574</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>185.123</v>
+        <v>169.77</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>79.355</v>
+        <v>72.012</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>207.756</v>
+        <v>208.028</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>86.449</v>
+        <v>80.203</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>212.8</v>
+        <v>194.662</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>279.904</v>
+        <v>269.019</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>204.314</v>
+        <v>187.761</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>285.606</v>
+        <v>274.54</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>205.084</v>
+        <v>186.793</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>68.105</v>
+        <v>68.288</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>42.077</v>
+        <v>39.35</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>64.968</v>
+        <v>64.71299999999999</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43.736</v>
+        <v>41.204</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>66.151</v>
+        <v>65.947</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>22.415</v>
+        <v>24.743</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>22.891</v>
+        <v>25.363</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.742</v>
+        <v>0.698</v>
       </c>
     </row>
     <row r="7">
@@ -935,70 +935,70 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>295.639</v>
+        <v>289.755</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>299.493</v>
+        <v>294.021</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>303.346</v>
+        <v>298.288</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>188.215</v>
+        <v>173.425</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>178.567</v>
+        <v>163.527</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>177.297</v>
+        <v>164.034</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>84.741</v>
+        <v>79.63200000000001</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>212.013</v>
+        <v>211.309</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>90.19799999999999</v>
+        <v>85.765</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>206.412</v>
+        <v>190.834</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>277.193</v>
+        <v>267.194</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>198.922</v>
+        <v>185.102</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>282.671</v>
+        <v>272.448</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>198.844</v>
+        <v>183.255</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>65.761</v>
+        <v>65.337</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>40.106</v>
+        <v>37.735</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>63.036</v>
+        <v>62.397</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>41.747</v>
+        <v>39.535</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>63.9</v>
+        <v>63.17</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>22.153</v>
+        <v>23.635</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>22.93</v>
+        <v>24.662</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.702</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="8">
@@ -1006,70 +1006,70 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>303.346</v>
+        <v>298.288</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>306.388</v>
+        <v>301.626</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>309.43</v>
+        <v>304.963</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>179.906</v>
+        <v>167.074</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>170.386</v>
+        <v>157.393</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>170.126</v>
+        <v>158.99</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>88.709</v>
+        <v>85.256</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>215.534</v>
+        <v>213.994</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>92.989</v>
+        <v>89.991</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>200.588</v>
+        <v>187.569</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>274.748</v>
+        <v>265.643</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>193.881</v>
+        <v>182.692</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>280.064</v>
+        <v>270.733</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>193.096</v>
+        <v>180.144</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>63.753</v>
+        <v>62.965</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>38.327</v>
+        <v>36.335</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>61.34</v>
+        <v>60.489</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>39.969</v>
+        <v>38.106</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>61.932</v>
+        <v>60.892</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>21.963</v>
+        <v>22.787</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>23.012</v>
+        <v>24.155</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="9">
@@ -1077,70 +1077,70 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>309.43</v>
+        <v>304.963</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>311.866</v>
+        <v>307.628</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>314.301</v>
+        <v>310.292</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>172.344</v>
+        <v>161.547</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>162.869</v>
+        <v>151.964</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>163.489</v>
+        <v>154.49</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>91.673</v>
+        <v>89.53</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>218.483</v>
+        <v>216.221</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>95.086</v>
+        <v>93.27500000000001</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>195.208</v>
+        <v>184.697</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>272.509</v>
+        <v>264.281</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>189.13</v>
+        <v>180.465</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>277.706</v>
+        <v>269.275</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>187.741</v>
+        <v>177.336</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>61.991</v>
+        <v>61.005</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>36.703</v>
+        <v>35.1</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>59.818</v>
+        <v>58.878</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>38.36</v>
+        <v>36.865</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>60.172</v>
+        <v>58.973</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>21.812</v>
+        <v>22.108</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>23.115</v>
+        <v>23.778</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.636</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="10">
@@ -1148,70 +1148,70 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>314.301</v>
+        <v>310.292</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>316.275</v>
+        <v>312.456</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>318.248</v>
+        <v>314.619</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>165.387</v>
+        <v>156.663</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>155.895</v>
+        <v>147.087</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>157.295</v>
+        <v>150.426</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>93.913</v>
+        <v>92.852</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>220.98</v>
+        <v>218.091</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>96.67100000000001</v>
+        <v>95.872</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>190.191</v>
+        <v>182.112</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>270.436</v>
+        <v>263.056</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>184.627</v>
+        <v>178.38</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>275.543</v>
+        <v>267.999</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>182.714</v>
+        <v>174.755</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>60.41</v>
+        <v>59.345</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>35.202</v>
+        <v>33.997</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>58.426</v>
+        <v>57.489</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>36.886</v>
+        <v>35.772</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>58.564</v>
+        <v>57.318</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>21.678</v>
+        <v>21.545</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>23.224</v>
+        <v>23.492</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.609</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="11">
@@ -1219,70 +1219,70 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>318.248</v>
+        <v>314.619</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>319.865</v>
+        <v>316.402</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>321.481</v>
+        <v>318.184</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>158.93</v>
+        <v>152.289</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>149.371</v>
+        <v>142.653</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>151.471</v>
+        <v>146.713</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>95.621</v>
+        <v>95.48099999999999</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>223.115</v>
+        <v>219.681</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>97.876</v>
+        <v>97.956</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>185.478</v>
+        <v>179.746</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>268.499</v>
+        <v>261.935</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>180.342</v>
+        <v>176.409</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>273.536</v>
+        <v>266.858</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>177.967</v>
+        <v>172.351</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>58.967</v>
+        <v>57.913</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>33.802</v>
+        <v>32.998</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>57.131</v>
+        <v>56.27</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>35.522</v>
+        <v>34.797</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>57.068</v>
+        <v>55.862</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>21.546</v>
+        <v>21.065</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>23.329</v>
+        <v>23.272</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.585</v>
+        <v>0.5639999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1290,70 +1290,70 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>321.481</v>
+        <v>318.184</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>321.481</v>
+        <v>318.184</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>321.481</v>
+        <v>318.184</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>150.081</v>
+        <v>145.115</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>141.75</v>
+        <v>136.88</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>145.203</v>
+        <v>142.448</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>96.931</v>
+        <v>97.593</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>224.55</v>
+        <v>220.591</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>96.931</v>
+        <v>97.593</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>178.662</v>
+        <v>174.879</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>265.548</v>
+        <v>259.609</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>174.584</v>
+        <v>172.673</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>270.087</v>
+        <v>264.043</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>171.723</v>
+        <v>168.109</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>57.143</v>
+        <v>56.078</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>32.263</v>
+        <v>31.82</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>56.275</v>
+        <v>55.584</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>33.757</v>
+        <v>33.339</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>55.635</v>
+        <v>54.512</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>21.878</v>
+        <v>21.173</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>24.012</v>
+        <v>23.764</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.541</v>
       </c>
     </row>
     <row r="13">
@@ -1361,70 +1361,70 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>321.481</v>
+        <v>318.184</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>321.481</v>
+        <v>318.184</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>321.481</v>
+        <v>318.184</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>142.993</v>
+        <v>140.037</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>134.303</v>
+        <v>131.403</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>138.4</v>
+        <v>137.59</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>92.877</v>
+        <v>93.979</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>215.745</v>
+        <v>211.478</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>92.877</v>
+        <v>93.979</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>170.508</v>
+        <v>168.649</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>254.132</v>
+        <v>248.977</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>166.675</v>
+        <v>166.623</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>269.642</v>
+        <v>264.345</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>170.931</v>
+        <v>169.272</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>56.995</v>
+        <v>56.134</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>31.903</v>
+        <v>31.855</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>56.135</v>
+        <v>55.666</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>32.026</v>
+        <v>31.989</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>51.787</v>
+        <v>50.921</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>19.761</v>
+        <v>18.933</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>24.233</v>
+        <v>23.811</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.543</v>
+        <v>0.528</v>
       </c>
     </row>
     <row r="14">
@@ -1432,70 +1432,70 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>321.481</v>
+        <v>318.184</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>321.481</v>
+        <v>318.184</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>321.481</v>
+        <v>318.184</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>136.395</v>
+        <v>135.655</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>127.342</v>
+        <v>126.632</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>127.342</v>
+        <v>126.632</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>85.76600000000001</v>
+        <v>87.235</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>203.567</v>
+        <v>199.131</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>85.76600000000001</v>
+        <v>87.235</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>161.119</v>
+        <v>161.283</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>240.116</v>
+        <v>235.985</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>153.531</v>
+        <v>153.771</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>272.333</v>
+        <v>267.843</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>173.55</v>
+        <v>173.808</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>57.838</v>
+        <v>57.256</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>32.028</v>
+        <v>32.453</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>56.04</v>
+        <v>55.438</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>30.055</v>
+        <v>30.429</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>47.202</v>
+        <v>46.767</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>17.146</v>
+        <v>16.338</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>24.011</v>
+        <v>22.984</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>0.534</v>
+        <v>0.522</v>
       </c>
     </row>
   </sheetData>
@@ -1659,70 +1659,70 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>288.407</v>
+        <v>274.664</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>292.75</v>
+        <v>281.068</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>297.259</v>
+        <v>287.983</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>196.344</v>
+        <v>156.341</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>190.344</v>
+        <v>150.341</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>185.419</v>
+        <v>151.492</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>104.749</v>
+        <v>89.819</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>192.51</v>
+        <v>198.164</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>104.749</v>
+        <v>89.819</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>222.538</v>
+        <v>180.306</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>270.723</v>
+        <v>248.74</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>212.962</v>
+        <v>176.117</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>274.975</v>
+        <v>252.412</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>217.263</v>
+        <v>175.129</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>61.92</v>
+        <v>60.122</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>44.676</v>
+        <v>37.187</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>60.537</v>
+        <v>59.336</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>45.565</v>
+        <v>38.272</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>61.175</v>
+        <v>59.144</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>15.611</v>
+        <v>20.873</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>15.861</v>
+        <v>22.15</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.866</v>
+        <v>0.786</v>
       </c>
     </row>
     <row r="3">
@@ -1730,70 +1730,70 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>297.259</v>
+        <v>287.983</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>301.636</v>
+        <v>293.561</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>306.148</v>
+        <v>299.398</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>185.419</v>
+        <v>151.492</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>179.086</v>
+        <v>145.158</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>177.971</v>
+        <v>148.185</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>103.632</v>
+        <v>92.854</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>202.516</v>
+        <v>206.544</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>103.632</v>
+        <v>92.854</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>212.414</v>
+        <v>177.684</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>270.341</v>
+        <v>252.451</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>205.945</v>
+        <v>174.873</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>274.578</v>
+        <v>256.145</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>206.909</v>
+        <v>172.316</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>60.799</v>
+        <v>58.495</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>41.487</v>
+        <v>35.099</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>59.788</v>
+        <v>57.928</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>42.477</v>
+        <v>36.259</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>59.943</v>
+        <v>57.394</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>17.467</v>
+        <v>21.136</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>18.301</v>
+        <v>22.829</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.824</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="4">
@@ -1801,70 +1801,70 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>306.148</v>
+        <v>299.398</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>309.83</v>
+        <v>303.787</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>313.591</v>
+        <v>308.299</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>177.971</v>
+        <v>148.185</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>171.304</v>
+        <v>141.519</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>171.441</v>
+        <v>145.286</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>102.875</v>
+        <v>94.628</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>210.716</v>
+        <v>213.671</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>102.875</v>
+        <v>94.628</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>205.565</v>
+        <v>175.822</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>271.563</v>
+        <v>256.287</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>199.938</v>
+        <v>173.386</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>275.817</v>
+        <v>260.028</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>199.821</v>
+        <v>170.241</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>59.97</v>
+        <v>57.439</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>39.11</v>
+        <v>33.517</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>59.034</v>
+        <v>56.923</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>40.184</v>
+        <v>34.742</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>59.013</v>
+        <v>56.231</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>18.829</v>
+        <v>21.489</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>19.924</v>
+        <v>23.406</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.787</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="5">
@@ -1872,70 +1872,70 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>313.591</v>
+        <v>308.299</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>316.444</v>
+        <v>311.563</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>319.338</v>
+        <v>314.884</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>171.441</v>
+        <v>145.286</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>164.441</v>
+        <v>138.286</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>165.444</v>
+        <v>142.624</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>104.644</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>214.694</v>
+        <v>216.375</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>104.644</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>200.854</v>
+        <v>175.534</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>270.433</v>
+        <v>256.79</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>195.761</v>
+        <v>173.337</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>274.746</v>
+        <v>260.626</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>194.914</v>
+        <v>169.786</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>58.601</v>
+        <v>55.861</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>37.45</v>
+        <v>32.583</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>57.686</v>
+        <v>55.367</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>38.609</v>
+        <v>33.88</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>57.529</v>
+        <v>54.536</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>18.92</v>
+        <v>20.656</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>20.237</v>
+        <v>22.785</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.745</v>
+        <v>0.6919999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1943,70 +1943,70 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>319.338</v>
+        <v>314.884</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>321.57</v>
+        <v>317.373</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>323.824</v>
+        <v>319.892</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>165.444</v>
+        <v>142.624</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>158.111</v>
+        <v>135.291</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>159.815</v>
+        <v>140.125</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>105.883</v>
+        <v>101.365</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>217.94</v>
+        <v>218.527</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>105.883</v>
+        <v>101.365</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>196.426</v>
+        <v>174.976</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>269.253</v>
+        <v>257.017</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>191.709</v>
+        <v>172.945</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>273.624</v>
+        <v>260.952</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>190.29</v>
+        <v>169.052</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>57.381</v>
+        <v>54.598</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>35.96</v>
+        <v>31.762</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>56.474</v>
+        <v>54.118</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>37.203</v>
+        <v>33.131</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>56.191</v>
+        <v>53.158</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>18.988</v>
+        <v>20.027</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>20.514</v>
+        <v>22.357</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.708</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="7">
@@ -2014,70 +2014,70 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>323.824</v>
+        <v>319.892</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>325.59</v>
+        <v>321.833</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>327.369</v>
+        <v>323.79</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>159.815</v>
+        <v>140.125</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>152.148</v>
+        <v>132.459</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>154.463</v>
+        <v>137.749</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>106.72</v>
+        <v>103.508</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>220.649</v>
+        <v>220.282</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>106.72</v>
+        <v>103.508</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>192.172</v>
+        <v>174.21</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>268.021</v>
+        <v>257.04</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>187.744</v>
+        <v>172.304</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>272.446</v>
+        <v>261.073</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>185.845</v>
+        <v>168.105</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>56.266</v>
+        <v>53.547</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>34.588</v>
+        <v>31.019</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>55.359</v>
+        <v>53.078</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>35.916</v>
+        <v>32.461</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>54.953</v>
+        <v>51.995</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>19.038</v>
+        <v>19.533</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>20.771</v>
+        <v>22.059</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.674</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="8">
@@ -2085,70 +2085,70 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>327.369</v>
+        <v>323.79</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>328.782</v>
+        <v>325.333</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>330.203</v>
+        <v>326.885</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>154.463</v>
+        <v>137.749</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>146.463</v>
+        <v>129.749</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>149.329</v>
+        <v>135.471</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>107.258</v>
+        <v>105.143</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>222.945</v>
+        <v>221.742</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>107.258</v>
+        <v>105.143</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>188.05</v>
+        <v>173.291</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>266.75</v>
+        <v>256.913</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>183.858</v>
+        <v>171.486</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>271.225</v>
+        <v>261.044</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>181.537</v>
+        <v>167.003</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>55.224</v>
+        <v>52.646</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>33.303</v>
+        <v>30.333</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>54.312</v>
+        <v>52.184</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>34.715</v>
+        <v>31.849</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>53.784</v>
+        <v>50.98</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>19.068</v>
+        <v>19.131</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>21.009</v>
+        <v>21.85</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.644</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="9">
@@ -2156,70 +2156,70 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>330.203</v>
+        <v>326.885</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>331.347</v>
+        <v>328.13</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>332.496</v>
+        <v>329.382</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>149.329</v>
+        <v>135.471</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>140.996</v>
+        <v>127.137</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>144.377</v>
+        <v>133.272</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>107.579</v>
+        <v>106.406</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>224.917</v>
+        <v>222.976</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>107.579</v>
+        <v>106.406</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>184.045</v>
+        <v>172.263</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>265.457</v>
+        <v>256.675</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>180.05</v>
+        <v>170.54</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>269.975</v>
+        <v>260.904</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>177.35</v>
+        <v>165.79</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>54.231</v>
+        <v>51.852</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>32.083</v>
+        <v>29.691</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>53.309</v>
+        <v>51.396</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>33.581</v>
+        <v>31.281</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>52.657</v>
+        <v>50.073</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>19.075</v>
+        <v>18.792</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>21.226</v>
+        <v>21.705</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.617</v>
+        <v>0.587</v>
       </c>
     </row>
     <row r="10">
@@ -2227,70 +2227,70 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>332.496</v>
+        <v>329.382</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>333.43</v>
+        <v>330.404</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>334.368</v>
+        <v>331.429</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>144.377</v>
+        <v>133.272</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>135.711</v>
+        <v>124.605</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>139.578</v>
+        <v>131.142</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>107.742</v>
+        <v>107.393</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>226.626</v>
+        <v>224.036</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>107.742</v>
+        <v>107.393</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>180.147</v>
+        <v>171.157</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>264.153</v>
+        <v>256.356</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>176.324</v>
+        <v>169.503</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>268.708</v>
+        <v>260.679</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>173.279</v>
+        <v>164.498</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>53.268</v>
+        <v>51.138</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>30.914</v>
+        <v>29.082</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>52.335</v>
+        <v>50.686</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>32.5</v>
+        <v>30.747</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>51.554</v>
+        <v>49.243</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>19.054</v>
+        <v>18.496</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>21.421</v>
+        <v>21.604</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.593</v>
+        <v>0.5669999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2298,70 +2298,70 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>334.368</v>
+        <v>331.429</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>335.138</v>
+        <v>332.276</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>335.91</v>
+        <v>333.126</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>139.578</v>
+        <v>131.142</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>130.578</v>
+        <v>122.142</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>134.91</v>
+        <v>129.069</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>107.791</v>
+        <v>108.169</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>228.119</v>
+        <v>224.957</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>107.791</v>
+        <v>108.169</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>176.354</v>
+        <v>169.996</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>262.848</v>
+        <v>255.977</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>172.683</v>
+        <v>168.403</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>267.433</v>
+        <v>260.391</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>169.32</v>
+        <v>163.154</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>52.322</v>
+        <v>50.483</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>29.787</v>
+        <v>28.5</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>51.376</v>
+        <v>50.035</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>31.461</v>
+        <v>30.241</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>50.461</v>
+        <v>48.472</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>19</v>
+        <v>18.231</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>21.589</v>
+        <v>21.535</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.571</v>
+        <v>0.549</v>
       </c>
     </row>
     <row r="12">
@@ -2369,70 +2369,70 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>335.91</v>
+        <v>333.126</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>335.284</v>
+        <v>332.424</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>334.66</v>
+        <v>331.723</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>134.91</v>
+        <v>129.069</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>125.577</v>
+        <v>119.736</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>129.461</v>
+        <v>126.063</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>106.033</v>
+        <v>106.872</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>228.626</v>
+        <v>224.851</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>106.033</v>
+        <v>106.872</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>171.592</v>
+        <v>167.573</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>260.844</v>
+        <v>254.744</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>167.342</v>
+        <v>165.268</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>265.463</v>
+        <v>259.262</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>164.355</v>
+        <v>160.494</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>51.834</v>
+        <v>50.374</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>28.778</v>
+        <v>28.036</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>50.681</v>
+        <v>49.71</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>30.544</v>
+        <v>29.857</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>49.823</v>
+        <v>48.249</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>19.279</v>
+        <v>18.392</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>21.903</v>
+        <v>21.674</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.55</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="13">
@@ -2440,70 +2440,70 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>334.66</v>
+        <v>331.723</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>334.176</v>
+        <v>331.172</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>333.692</v>
+        <v>330.622</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>129.461</v>
+        <v>126.063</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>119.795</v>
+        <v>116.396</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>124.37</v>
+        <v>123.339</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>100.987</v>
+        <v>102.159</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>219.358</v>
+        <v>215.238</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>100.987</v>
+        <v>102.159</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>164.19</v>
+        <v>162.26</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>249.937</v>
+        <v>244.695</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>160.207</v>
+        <v>160.153</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>266.293</v>
+        <v>260.935</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>165.599</v>
+        <v>163.895</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>52.044</v>
+        <v>50.979</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>28.64</v>
+        <v>28.404</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>50.924</v>
+        <v>50.366</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>29.089</v>
+        <v>28.889</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>46.336</v>
+        <v>45.25</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>17.247</v>
+        <v>16.361</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>22.284</v>
+        <v>21.962</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.536</v>
+        <v>0.521</v>
       </c>
     </row>
     <row r="14">
@@ -2511,70 +2511,70 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>333.692</v>
+        <v>330.622</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>333.498</v>
+        <v>330.476</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>333.305</v>
+        <v>330.329</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>124.37</v>
+        <v>123.339</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>114.37</v>
+        <v>113.339</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>114.37</v>
+        <v>113.339</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>93.176</v>
+        <v>94.75700000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>206.798</v>
+        <v>202.539</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>93.176</v>
+        <v>94.75700000000001</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>155.402</v>
+        <v>155.536</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>236.318</v>
+        <v>232.095</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>147.52</v>
+        <v>147.732</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>270.425</v>
+        <v>265.908</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>170.542</v>
+        <v>170.81</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>53.16</v>
+        <v>52.466</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>28.945</v>
+        <v>29.231</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>50.831</v>
+        <v>50.103</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>27.381</v>
+        <v>27.635</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>42.116</v>
+        <v>41.57</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>14.735</v>
+        <v>13.935</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>21.886</v>
+        <v>20.872</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>0.531</v>
+        <v>0.518</v>
       </c>
     </row>
   </sheetData>
@@ -2738,70 +2738,70 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>146.873</v>
+        <v>74.54900000000001</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>138.75</v>
+        <v>60.971</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>131.914</v>
+        <v>63.755</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>137.577</v>
+        <v>128.809</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>212.168</v>
+        <v>218.617</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>137.577</v>
+        <v>128.809</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>201.244</v>
+        <v>148.826</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>253.509</v>
+        <v>226.96</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>190.601</v>
+        <v>143.723</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>258.045</v>
+        <v>230.978</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>195.395</v>
+        <v>142.51</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>46.872</v>
+        <v>30.06</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>33.183</v>
+        <v>15.584</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>43.796</v>
+        <v>26.333</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>34.693</v>
+        <v>18.83</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>45.243</v>
+        <v>25.33</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>10.55</v>
+        <v>6.501</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>10.613</v>
+        <v>10.75</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.806</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="3">
@@ -2809,70 +2809,70 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>141.714</v>
+        <v>86.122</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>133.321</v>
+        <v>74.42</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>131.819</v>
+        <v>80.163</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>131.593</v>
+        <v>124.726</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>218.151</v>
+        <v>222.7</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>131.593</v>
+        <v>124.726</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>193.39</v>
+        <v>151.57</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>255.664</v>
+        <v>234.805</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>186.261</v>
+        <v>148.266</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>260.14</v>
+        <v>238.772</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>187.327</v>
+        <v>145.241</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>47.121</v>
+        <v>34.625</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>31.431</v>
+        <v>18.478</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>45.049</v>
+        <v>32.73</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>33.008</v>
+        <v>21.142</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>45.374</v>
+        <v>30.823</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>12.365</v>
+        <v>9.680999999999999</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>13.618</v>
+        <v>14.251</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.775</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="4">
@@ -2880,70 +2880,70 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>140.295</v>
+        <v>95.55500000000001</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>131.736</v>
+        <v>84.849</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>131.914</v>
+        <v>90.995</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>126.526</v>
+        <v>120.894</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>223.219</v>
+        <v>226.531</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>126.526</v>
+        <v>120.894</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>188.922</v>
+        <v>154.098</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>259.193</v>
+        <v>241.901</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>182.784</v>
+        <v>151.312</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>263.647</v>
+        <v>245.86</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>182.656</v>
+        <v>147.698</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>47.954</v>
+        <v>38.323</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>30.548</v>
+        <v>20.534</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>46.194</v>
+        <v>36.968</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>32.15</v>
+        <v>22.871</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>46.156</v>
+        <v>35.063</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>14.006</v>
+        <v>12.192</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>15.647</v>
+        <v>16.434</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.748</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2951,70 +2951,70 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>138.635</v>
+        <v>101.646</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>129.879</v>
+        <v>91.36199999999999</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>131.147</v>
+        <v>97.803</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>124.632</v>
+        <v>120.3</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>225.113</v>
+        <v>227.125</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>124.632</v>
+        <v>120.3</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>186.421</v>
+        <v>157.493</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>259.893</v>
+        <v>244.812</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>180.921</v>
+        <v>155.041</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>264.378</v>
+        <v>248.833</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>180.004</v>
+        <v>151.06</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>48.045</v>
+        <v>40.196</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>29.983</v>
+        <v>21.913</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>46.459</v>
+        <v>39.111</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>31.627</v>
+        <v>24.11</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>46.181</v>
+        <v>37.215</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>14.554</v>
+        <v>13.105</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>16.476</v>
+        <v>17.198</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.714</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="6">
@@ -3022,70 +3022,70 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>136.536</v>
+        <v>105.617</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>127.551</v>
+        <v>95.483</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>129.658</v>
+        <v>102.218</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>122.996</v>
+        <v>119.774</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>226.748</v>
+        <v>227.651</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>122.996</v>
+        <v>119.774</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>183.767</v>
+        <v>159.69</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>260.162</v>
+        <v>246.864</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>178.716</v>
+        <v>157.462</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>264.683</v>
+        <v>250.958</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>177.193</v>
+        <v>153.176</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>47.986</v>
+        <v>41.406</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>29.359</v>
+        <v>22.754</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>46.51</v>
+        <v>40.478</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>31.054</v>
+        <v>24.889</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>46.042</v>
+        <v>38.561</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>14.987</v>
+        <v>13.673</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>17.152</v>
+        <v>17.724</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="7">
@@ -3093,70 +3093,70 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>134.035</v>
+        <v>108.18</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>124.794</v>
+        <v>98.047</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>127.605</v>
+        <v>105.084</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>121.552</v>
+        <v>119.298</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>228.192</v>
+        <v>228.128</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>121.552</v>
+        <v>119.298</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>180.943</v>
+        <v>161.043</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>260.087</v>
+        <v>248.305</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>176.233</v>
+        <v>158.98</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>264.645</v>
+        <v>252.478</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>174.208</v>
+        <v>154.419</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>47.796</v>
+        <v>42.202</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>28.673</v>
+        <v>23.257</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>46.392</v>
+        <v>41.375</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>30.429</v>
+        <v>25.371</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>45.754</v>
+        <v>39.416</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>15.325</v>
+        <v>14.045</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>17.718</v>
+        <v>18.118</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.653</v>
+        <v>0.611</v>
       </c>
     </row>
     <row r="8">
@@ -3164,70 +3164,70 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>131.206</v>
+        <v>109.77</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>121.687</v>
+        <v>99.54600000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>125.123</v>
+        <v>106.896</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>120.261</v>
+        <v>118.86</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>229.484</v>
+        <v>228.565</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>120.261</v>
+        <v>118.86</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>177.983</v>
+        <v>161.793</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>259.751</v>
+        <v>249.302</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>173.547</v>
+        <v>159.858</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>264.344</v>
+        <v>253.558</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>171.086</v>
+        <v>155.039</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>47.492</v>
+        <v>42.723</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>27.935</v>
+        <v>23.534</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>46.135</v>
+        <v>41.966</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>29.759</v>
+        <v>25.653</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>45.338</v>
+        <v>39.946</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>15.579</v>
+        <v>14.293</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>18.2</v>
+        <v>18.432</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.627</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="9">
@@ -3235,70 +3235,70 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>128.122</v>
+        <v>110.664</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>118.304</v>
+        <v>100.29</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>122.314</v>
+        <v>107.961</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>119.097</v>
+        <v>118.455</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>230.648</v>
+        <v>228.971</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>119.097</v>
+        <v>118.455</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>174.927</v>
+        <v>162.105</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>259.218</v>
+        <v>249.971</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>170.719</v>
+        <v>160.272</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>263.844</v>
+        <v>254.311</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>167.869</v>
+        <v>155.208</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>47.091</v>
+        <v>43.052</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>27.154</v>
+        <v>23.654</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>45.764</v>
+        <v>42.346</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>29.052</v>
+        <v>25.795</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>44.809</v>
+        <v>40.253</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>15.757</v>
+        <v>14.458</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>18.609</v>
+        <v>18.693</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.602</v>
+        <v>0.571</v>
       </c>
     </row>
     <row r="10">
@@ -3306,70 +3306,70 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>124.84</v>
+        <v>111.048</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>114.706</v>
+        <v>100.482</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>119.257</v>
+        <v>108.482</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>118.044</v>
+        <v>118.077</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>231.701</v>
+        <v>229.349</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>118.044</v>
+        <v>118.077</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>171.812</v>
+        <v>162.092</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>258.54</v>
+        <v>250.395</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>167.799</v>
+        <v>160.345</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>263.193</v>
+        <v>254.819</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>164.596</v>
+        <v>155.045</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46.603</v>
+        <v>43.243</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>26.338</v>
+        <v>23.659</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>45.293</v>
+        <v>42.575</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>28.316</v>
+        <v>25.836</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>44.179</v>
+        <v>40.398</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>15.863</v>
+        <v>14.562</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>18.955</v>
+        <v>18.916</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.58</v>
+        <v>0.553</v>
       </c>
     </row>
     <row r="11">
@@ -3377,70 +3377,70 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>121.405</v>
+        <v>111.051</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>110.94</v>
+        <v>100.263</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>116.008</v>
+        <v>108.596</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>117.088</v>
+        <v>117.723</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>232.657</v>
+        <v>229.703</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>117.088</v>
+        <v>117.723</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>168.667</v>
+        <v>161.836</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>257.754</v>
+        <v>250.632</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>164.825</v>
+        <v>160.161</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>262.428</v>
+        <v>255.139</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>161.299</v>
+        <v>154.633</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46.037</v>
+        <v>43.33</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>25.494</v>
+        <v>23.581</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>44.735</v>
+        <v>42.691</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>27.556</v>
+        <v>25.802</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>43.456</v>
+        <v>40.421</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>15.899</v>
+        <v>14.619</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>19.241</v>
+        <v>19.11</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.537</v>
       </c>
     </row>
     <row r="12">
@@ -3448,70 +3448,70 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>349.745</v>
+        <v>347.426</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>348.542</v>
+        <v>346.078</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>347.339</v>
+        <v>344.731</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>114.187</v>
+        <v>106.427</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>105.011</v>
+        <v>97.32299999999999</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>111.519</v>
+        <v>107.203</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>116.22</v>
+        <v>117.39</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>233.126</v>
+        <v>229.581</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>114.61</v>
+        <v>115.602</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>162.928</v>
+        <v>158.452</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>255.686</v>
+        <v>249.358</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>159.913</v>
+        <v>157.659</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>259.947</v>
+        <v>253.463</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>156.039</v>
+        <v>151.8</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>44.495</v>
+        <v>42.196</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>24.249</v>
+        <v>22.973</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>44.217</v>
+        <v>42.841</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>26.057</v>
+        <v>24.828</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>42.298</v>
+        <v>39.876</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>16.24</v>
+        <v>15.048</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>19.968</v>
+        <v>19.868</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.537</v>
+        <v>0.519</v>
       </c>
     </row>
     <row r="13">
@@ -3519,70 +3519,70 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>347.339</v>
+        <v>344.731</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>346.406</v>
+        <v>343.67</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>345.472</v>
+        <v>342.609</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>111.703</v>
+        <v>107.244</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>101.816</v>
+        <v>97.437</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>108.541</v>
+        <v>107.21</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>109.862</v>
+        <v>111.245</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>223.288</v>
+        <v>219.354</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>108.659</v>
+        <v>109.891</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>156.676</v>
+        <v>154.521</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>245.406</v>
+        <v>240.022</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>153.584</v>
+        <v>153.525</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>262.436</v>
+        <v>256.937</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>159.764</v>
+        <v>157.951</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>45.476</v>
+        <v>43.951</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>24.512</v>
+        <v>23.951</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>44.969</v>
+        <v>44.293</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>25.191</v>
+        <v>24.67</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>39.59</v>
+        <v>38.089</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>14.399</v>
+        <v>13.419</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>20.457</v>
+        <v>20.342</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.528</v>
+        <v>0.512</v>
       </c>
     </row>
     <row r="14">
@@ -3590,70 +3590,70 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>345.472</v>
+        <v>342.609</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>345.098</v>
+        <v>342.326</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>344.723</v>
+        <v>342.043</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>110.104</v>
+        <v>108.931</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>99.19799999999999</v>
+        <v>97.86499999999999</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>99.724</v>
+        <v>98.265</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>100.652</v>
+        <v>102.214</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>210.164</v>
+        <v>206.049</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>100.196</v>
+        <v>101.874</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>149.177</v>
+        <v>149.377</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>232.399</v>
+        <v>228.109</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>141.366</v>
+        <v>141.542</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>268.44</v>
+        <v>263.923</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>167.474</v>
+        <v>167.776</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>47.568</v>
+        <v>46.822</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>25.268</v>
+        <v>25.406</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>44.865</v>
+        <v>43.967</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>24.215</v>
+        <v>24.377</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>36.322</v>
+        <v>35.683</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>12.107</v>
+        <v>11.307</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>19.597</v>
+        <v>18.561</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>0.526</v>
+        <v>0.514</v>
       </c>
     </row>
   </sheetData>

--- a/export/Приложение_Б.xlsx
+++ b/export/Приложение_Б.xlsx
@@ -580,70 +580,70 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>173.713</v>
+        <v>192.285</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>193.116</v>
+        <v>208.146</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>212.519</v>
+        <v>224.006</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>225.437</v>
+        <v>231.879</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>213.126</v>
+        <v>220.408</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>204.536</v>
+        <v>211.747</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>-2.951</v>
+        <v>19.13</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>177.342</v>
+        <v>175.217</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>32.851</v>
+        <v>45.896</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>225.456</v>
+        <v>232.667</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>277.26</v>
+        <v>281.568</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>207.157</v>
+        <v>216.664</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>286.412</v>
+        <v>289.397</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>213.709</v>
+        <v>222.854</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>90.75</v>
+        <v>85.28400000000001</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>50.236</v>
+        <v>51.516</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>80.876</v>
+        <v>77.77</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>51.916</v>
+        <v>53.25</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>85.767</v>
+        <v>81.503</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>33.851</v>
+        <v>28.253</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>30.639</v>
+        <v>26.254</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.908</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="3">
@@ -651,70 +651,70 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>212.519</v>
+        <v>224.006</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>227.269</v>
+        <v>237.051</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>242.02</v>
+        <v>250.097</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>212.573</v>
+        <v>218.927</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>200.162</v>
+        <v>207.093</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>193.627</v>
+        <v>200.53</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>26.176</v>
+        <v>38.759</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>188.521</v>
+        <v>187.739</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>50.688</v>
+        <v>59.445</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>214.178</v>
+        <v>222.332</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>274.963</v>
+        <v>279.523</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>200.152</v>
+        <v>209.155</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>282.685</v>
+        <v>286.785</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>203.878</v>
+        <v>212.883</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>82.98</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>46.716</v>
+        <v>47.806</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>75.33</v>
+        <v>73.488</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>48.762</v>
+        <v>49.764</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>79.044</v>
+        <v>76.60599999999999</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>30.282</v>
+        <v>26.843</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>28.615</v>
+        <v>25.682</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.844</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="4">
@@ -722,70 +722,70 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>242.02</v>
+        <v>250.097</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>252.722</v>
+        <v>259.859</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>263.424</v>
+        <v>269.622</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>200.49</v>
+        <v>206.758</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>188.726</v>
+        <v>195.407</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>184.218</v>
+        <v>190.707</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45.188</v>
+        <v>53.653</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>198.973</v>
+        <v>198.643</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>62.05</v>
+        <v>68.586</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>205.519</v>
+        <v>213.606</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>274.24</v>
+        <v>278.645</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>194.387</v>
+        <v>202.665</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>280.961</v>
+        <v>285.2</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>196.231</v>
+        <v>204.771</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>77.29900000000001</v>
+        <v>75.453</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>43.486</v>
+        <v>44.529</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>71.38500000000001</v>
+        <v>70.21899999999999</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>45.527</v>
+        <v>46.465</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>74.10299999999999</v>
+        <v>72.605</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>28.576</v>
+        <v>26.14</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>27.899</v>
+        <v>25.69</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.793</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -793,70 +793,70 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>263.424</v>
+        <v>269.622</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>270.995</v>
+        <v>276.647</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>278.567</v>
+        <v>283.673</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>189.706</v>
+        <v>195.736</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>178.829</v>
+        <v>185.134</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>176.403</v>
+        <v>182.363</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>61.267</v>
+        <v>67.34399999999999</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>203.975</v>
+        <v>204.077</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>72.66800000000001</v>
+        <v>77.711</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>199.353</v>
+        <v>206.997</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>271.267</v>
+        <v>275.539</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>190.784</v>
+        <v>198.231</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>277.229</v>
+        <v>281.476</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>190.976</v>
+        <v>198.849</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>72.102</v>
+        <v>71.014</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>41.242</v>
+        <v>42.214</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>67.611</v>
+        <v>66.919</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43.18</v>
+        <v>44.058</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>69.455</v>
+        <v>68.595</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>26.275</v>
+        <v>24.537</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>26.369</v>
+        <v>24.706</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.74</v>
+        <v>0.757</v>
       </c>
     </row>
     <row r="6">
@@ -864,70 +864,70 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>278.567</v>
+        <v>283.673</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>284.161</v>
+        <v>288.916</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>289.755</v>
+        <v>294.159</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>180.852</v>
+        <v>186.47</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>170.574</v>
+        <v>176.376</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>169.77</v>
+        <v>175.131</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>72.012</v>
+        <v>76.678</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>208.028</v>
+        <v>208.434</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>80.203</v>
+        <v>84.24299999999999</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>194.662</v>
+        <v>201.62</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>269.019</v>
+        <v>273.045</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>187.761</v>
+        <v>194.339</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>274.54</v>
+        <v>278.6</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>186.793</v>
+        <v>193.87</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>68.288</v>
+        <v>67.64700000000001</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>39.35</v>
+        <v>40.238</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>64.71299999999999</v>
+        <v>64.31100000000001</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>41.204</v>
+        <v>42.014</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>65.947</v>
+        <v>65.47199999999999</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>24.743</v>
+        <v>23.459</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>25.363</v>
+        <v>24.073</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.698</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="7">
@@ -935,70 +935,70 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>289.755</v>
+        <v>294.159</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>294.021</v>
+        <v>298.182</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>298.288</v>
+        <v>302.205</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>173.425</v>
+        <v>178.523</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>163.527</v>
+        <v>168.75</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>164.034</v>
+        <v>168.751</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>79.63200000000001</v>
+        <v>83.349</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>211.309</v>
+        <v>211.961</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>85.765</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>190.834</v>
+        <v>197.022</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>267.194</v>
+        <v>270.932</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>185.102</v>
+        <v>190.814</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>272.448</v>
+        <v>276.245</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>183.255</v>
+        <v>189.501</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>65.337</v>
+        <v>64.973</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>37.735</v>
+        <v>38.525</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>62.397</v>
+        <v>62.174</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>39.535</v>
+        <v>40.259</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>63.17</v>
+        <v>62.936</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>23.635</v>
+        <v>22.676</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>24.662</v>
+        <v>23.65</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.663</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="8">
@@ -1006,70 +1006,70 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>298.288</v>
+        <v>302.205</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>301.626</v>
+        <v>305.363</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>304.963</v>
+        <v>308.521</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>167.074</v>
+        <v>171.584</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>157.393</v>
+        <v>161.99</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>158.99</v>
+        <v>163.036</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>85.256</v>
+        <v>88.279</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>213.994</v>
+        <v>214.856</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>89.991</v>
+        <v>92.723</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>187.569</v>
+        <v>192.962</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>265.643</v>
+        <v>269.08</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>182.692</v>
+        <v>187.559</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>270.733</v>
+        <v>274.237</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>180.144</v>
+        <v>185.56</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>62.965</v>
+        <v>62.774</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>36.335</v>
+        <v>37.014</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>60.489</v>
+        <v>60.372</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>38.106</v>
+        <v>38.732</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>60.892</v>
+        <v>60.807</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>22.787</v>
+        <v>22.075</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>24.155</v>
+        <v>23.358</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.633</v>
+        <v>0.645</v>
       </c>
     </row>
     <row r="9">
@@ -1077,70 +1077,70 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>304.963</v>
+        <v>308.521</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>307.628</v>
+        <v>311.047</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>310.292</v>
+        <v>313.572</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>161.547</v>
+        <v>165.427</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>151.964</v>
+        <v>155.907</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>154.49</v>
+        <v>157.85</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>89.53</v>
+        <v>92.01300000000001</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>216.221</v>
+        <v>217.266</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>93.27500000000001</v>
+        <v>95.541</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>184.697</v>
+        <v>189.295</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>264.281</v>
+        <v>267.416</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>180.465</v>
+        <v>184.512</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>269.275</v>
+        <v>272.474</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>177.336</v>
+        <v>181.939</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>61.005</v>
+        <v>60.917</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>35.1</v>
+        <v>35.663</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>58.878</v>
+        <v>58.815</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>36.865</v>
+        <v>37.382</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>58.973</v>
+        <v>58.972</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>22.108</v>
+        <v>21.59</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>23.778</v>
+        <v>23.152</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.607</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="10">
@@ -1148,70 +1148,70 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>310.292</v>
+        <v>313.572</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>312.456</v>
+        <v>315.623</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>314.619</v>
+        <v>317.674</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>156.663</v>
+        <v>159.888</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>147.087</v>
+        <v>150.361</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>150.426</v>
+        <v>153.091</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>92.852</v>
+        <v>94.89700000000001</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>218.091</v>
+        <v>219.298</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>95.872</v>
+        <v>97.747</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>182.112</v>
+        <v>185.929</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>263.056</v>
+        <v>265.895</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>178.38</v>
+        <v>181.635</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>267.999</v>
+        <v>270.893</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>174.755</v>
+        <v>178.569</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>59.345</v>
+        <v>59.31</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>33.997</v>
+        <v>34.436</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>57.489</v>
+        <v>57.442</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>35.772</v>
+        <v>36.173</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>57.318</v>
+        <v>57.355</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>21.545</v>
+        <v>21.182</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>23.492</v>
+        <v>23.006</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.584</v>
+        <v>0.593</v>
       </c>
     </row>
     <row r="11">
@@ -1219,70 +1219,70 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>314.619</v>
+        <v>317.674</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>316.402</v>
+        <v>319.363</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>318.184</v>
+        <v>321.051</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>152.289</v>
+        <v>154.842</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>142.653</v>
+        <v>145.248</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>146.713</v>
+        <v>148.68</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>95.48099999999999</v>
+        <v>97.15900000000001</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>219.681</v>
+        <v>221.033</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>97.956</v>
+        <v>99.496</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>179.746</v>
+        <v>182.8</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>261.935</v>
+        <v>264.486</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>176.409</v>
+        <v>178.9</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>266.858</v>
+        <v>269.449</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>172.351</v>
+        <v>175.401</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>57.913</v>
+        <v>57.893</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>32.998</v>
+        <v>33.31</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>56.27</v>
+        <v>56.21</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>34.797</v>
+        <v>35.076</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>55.862</v>
+        <v>55.903</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>21.065</v>
+        <v>20.827</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>23.272</v>
+        <v>22.9</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="12">
@@ -1290,70 +1290,70 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>318.184</v>
+        <v>321.051</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>318.184</v>
+        <v>321.051</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>318.184</v>
+        <v>321.051</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>145.115</v>
+        <v>147.18</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>136.88</v>
+        <v>138.897</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>142.448</v>
+        <v>143.757</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>97.593</v>
+        <v>98.956</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>220.591</v>
+        <v>222.095</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>97.593</v>
+        <v>98.956</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>174.879</v>
+        <v>177.353</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>259.609</v>
+        <v>261.952</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>172.673</v>
+        <v>174.523</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>264.043</v>
+        <v>266.436</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>168.109</v>
+        <v>170.543</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>56.078</v>
+        <v>56.085</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>31.82</v>
+        <v>32.022</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>55.584</v>
+        <v>55.458</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>33.339</v>
+        <v>33.532</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>54.512</v>
+        <v>54.532</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>21.173</v>
+        <v>21</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>23.764</v>
+        <v>23.436</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.541</v>
+        <v>0.549</v>
       </c>
     </row>
     <row r="13">
@@ -1361,70 +1361,70 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>318.184</v>
+        <v>321.051</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>318.184</v>
+        <v>321.051</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>318.184</v>
+        <v>321.051</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>140.037</v>
+        <v>141.443</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>131.403</v>
+        <v>132.777</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>137.59</v>
+        <v>138.258</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>93.979</v>
+        <v>95.137</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>211.478</v>
+        <v>213.072</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>93.979</v>
+        <v>95.137</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>168.649</v>
+        <v>170.462</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>248.977</v>
+        <v>251.057</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>166.623</v>
+        <v>167.828</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>264.345</v>
+        <v>266.54</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>169.272</v>
+        <v>171.141</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>56.134</v>
+        <v>56.075</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>31.855</v>
+        <v>31.929</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>55.666</v>
+        <v>55.468</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>31.989</v>
+        <v>32.05</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>50.921</v>
+        <v>50.881</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>18.933</v>
+        <v>18.83</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>23.811</v>
+        <v>23.539</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.528</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="14">
@@ -1432,70 +1432,70 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>318.184</v>
+        <v>321.051</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>318.184</v>
+        <v>321.051</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>318.184</v>
+        <v>321.051</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>135.655</v>
+        <v>136.31</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>126.632</v>
+        <v>127.264</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>126.632</v>
+        <v>127.264</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>87.235</v>
+        <v>88.188</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>199.131</v>
+        <v>200.758</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>87.235</v>
+        <v>88.188</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>161.283</v>
+        <v>162.35</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>235.985</v>
+        <v>237.697</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>153.771</v>
+        <v>154.833</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>267.843</v>
+        <v>269.825</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>173.808</v>
+        <v>175.119</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>57.256</v>
+        <v>57.098</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>32.453</v>
+        <v>32.371</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>55.438</v>
+        <v>55.28</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>30.429</v>
+        <v>30.343</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>46.767</v>
+        <v>46.613</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>16.338</v>
+        <v>16.27</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>22.984</v>
+        <v>22.908</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>0.522</v>
+        <v>0.528</v>
       </c>
     </row>
   </sheetData>
@@ -1659,70 +1659,70 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>274.664</v>
+        <v>282.135</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>281.068</v>
+        <v>287.708</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>287.983</v>
+        <v>293.603</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>156.341</v>
+        <v>170.744</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>150.341</v>
+        <v>164.744</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>151.492</v>
+        <v>163.782</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>89.819</v>
+        <v>96.36499999999999</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>198.164</v>
+        <v>197.238</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>89.819</v>
+        <v>96.36499999999999</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>180.306</v>
+        <v>196.06</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>248.74</v>
+        <v>256.989</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>176.117</v>
+        <v>190.028</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>252.412</v>
+        <v>260.876</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>175.129</v>
+        <v>190.858</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>60.122</v>
+        <v>60.56</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>37.187</v>
+        <v>39.87</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>59.336</v>
+        <v>59.529</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>38.272</v>
+        <v>40.882</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>59.144</v>
+        <v>59.675</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>20.873</v>
+        <v>18.793</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>22.15</v>
+        <v>19.658</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.786</v>
+        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1730,70 +1730,70 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>287.983</v>
+        <v>293.603</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>293.561</v>
+        <v>298.681</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>299.398</v>
+        <v>303.953</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>151.492</v>
+        <v>163.782</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>145.158</v>
+        <v>157.449</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>148.185</v>
+        <v>159.036</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>92.854</v>
+        <v>97.998</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>206.544</v>
+        <v>205.956</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>92.854</v>
+        <v>97.998</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>177.684</v>
+        <v>190.862</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>252.451</v>
+        <v>259.245</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>174.873</v>
+        <v>186.805</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>256.145</v>
+        <v>263.139</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>172.316</v>
+        <v>185.455</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>58.495</v>
+        <v>59.106</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>35.099</v>
+        <v>37.397</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>57.928</v>
+        <v>58.359</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>36.259</v>
+        <v>38.493</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>57.394</v>
+        <v>58.101</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>21.136</v>
+        <v>19.609</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>22.829</v>
+        <v>20.961</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.755</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="4">
@@ -1801,70 +1801,70 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>299.398</v>
+        <v>303.953</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>303.787</v>
+        <v>308.021</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>308.299</v>
+        <v>312.188</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>148.185</v>
+        <v>159.036</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>141.519</v>
+        <v>152.369</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>145.286</v>
+        <v>154.875</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>94.628</v>
+        <v>98.899</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>213.671</v>
+        <v>213.29</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>94.628</v>
+        <v>98.899</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>175.822</v>
+        <v>187.279</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>256.287</v>
+        <v>262.124</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>173.386</v>
+        <v>183.758</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>260.028</v>
+        <v>266.054</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>170.241</v>
+        <v>181.652</v>
       </c>
       <c r="P4" s="2" t="n">
+        <v>58.124</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>35.541</v>
+      </c>
+      <c r="R4" s="2" t="n">
         <v>57.439</v>
       </c>
-      <c r="Q4" s="2" t="n">
-        <v>33.517</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>56.923</v>
-      </c>
       <c r="S4" s="2" t="n">
-        <v>34.742</v>
+        <v>36.709</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>56.231</v>
+        <v>57.014</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>21.489</v>
+        <v>20.304</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>23.406</v>
+        <v>21.898</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.727</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="5">
@@ -1872,70 +1872,70 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>308.299</v>
+        <v>312.188</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>311.563</v>
+        <v>315.247</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>314.884</v>
+        <v>318.353</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>145.286</v>
+        <v>154.875</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>138.286</v>
+        <v>147.875</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>142.624</v>
+        <v>151.054</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>98.51000000000001</v>
+        <v>102.037</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>216.375</v>
+        <v>216.316</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>98.51000000000001</v>
+        <v>102.037</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>175.534</v>
+        <v>185.466</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>256.79</v>
+        <v>262.03</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>173.337</v>
+        <v>182.288</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>260.626</v>
+        <v>266.043</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>169.786</v>
+        <v>179.662</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>55.861</v>
+        <v>56.622</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>32.583</v>
+        <v>34.357</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>55.367</v>
+        <v>55.961</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>33.88</v>
+        <v>35.601</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>54.536</v>
+        <v>55.393</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>20.656</v>
+        <v>19.792</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>22.785</v>
+        <v>21.604</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="6">
@@ -1943,70 +1943,70 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>314.884</v>
+        <v>318.353</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>317.373</v>
+        <v>320.702</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>319.892</v>
+        <v>323.076</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>142.624</v>
+        <v>151.054</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>135.291</v>
+        <v>143.72</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>140.125</v>
+        <v>147.466</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>101.365</v>
+        <v>104.326</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>218.527</v>
+        <v>218.75</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>101.365</v>
+        <v>104.326</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>174.976</v>
+        <v>183.579</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>257.017</v>
+        <v>261.739</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>172.945</v>
+        <v>180.639</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>260.952</v>
+        <v>265.836</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>169.052</v>
+        <v>177.593</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>54.598</v>
+        <v>55.369</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>31.762</v>
+        <v>33.305</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>54.118</v>
+        <v>54.722</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>33.131</v>
+        <v>34.626</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>53.158</v>
+        <v>54.024</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>20.027</v>
+        <v>19.398</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>22.357</v>
+        <v>21.417</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.66</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="7">
@@ -2014,70 +2014,70 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>319.892</v>
+        <v>323.076</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>321.833</v>
+        <v>324.915</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>323.79</v>
+        <v>326.768</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>140.125</v>
+        <v>147.466</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>132.459</v>
+        <v>139.8</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>137.749</v>
+        <v>144.056</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>103.508</v>
+        <v>106.014</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>220.282</v>
+        <v>220.754</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>103.508</v>
+        <v>106.014</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>174.21</v>
+        <v>181.619</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>257.04</v>
+        <v>261.298</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>172.304</v>
+        <v>178.86</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>261.073</v>
+        <v>265.479</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>168.105</v>
+        <v>175.451</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>53.547</v>
+        <v>54.288</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>31.019</v>
+        <v>32.345</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>53.078</v>
+        <v>53.65</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>32.461</v>
+        <v>33.743</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>51.995</v>
+        <v>52.826</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>19.533</v>
+        <v>19.083</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>22.059</v>
+        <v>21.304</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.633</v>
+        <v>0.648</v>
       </c>
     </row>
     <row r="8">
@@ -2085,70 +2085,70 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>323.79</v>
+        <v>326.768</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>325.333</v>
+        <v>328.233</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>326.885</v>
+        <v>329.706</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>137.749</v>
+        <v>144.056</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>129.749</v>
+        <v>136.056</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>135.471</v>
+        <v>140.785</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>105.143</v>
+        <v>107.269</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>221.742</v>
+        <v>222.437</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>105.143</v>
+        <v>107.269</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>173.291</v>
+        <v>179.607</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>256.913</v>
+        <v>260.748</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>171.486</v>
+        <v>176.994</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>261.044</v>
+        <v>265.01</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>167.003</v>
+        <v>173.257</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>52.646</v>
+        <v>53.327</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>30.333</v>
+        <v>31.452</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>52.184</v>
+        <v>52.695</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>31.849</v>
+        <v>32.928</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>50.98</v>
+        <v>51.747</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>19.131</v>
+        <v>18.819</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>21.85</v>
+        <v>21.242</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.609</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="9">
@@ -2156,70 +2156,70 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>326.885</v>
+        <v>329.706</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>328.13</v>
+        <v>330.891</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>329.382</v>
+        <v>332.08</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>135.471</v>
+        <v>140.785</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>127.137</v>
+        <v>132.451</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>133.272</v>
+        <v>137.629</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>106.406</v>
+        <v>108.208</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>222.976</v>
+        <v>223.872</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>106.406</v>
+        <v>108.208</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>172.263</v>
+        <v>177.565</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>256.675</v>
+        <v>260.119</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>170.54</v>
+        <v>175.073</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>260.904</v>
+        <v>264.46</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>165.79</v>
+        <v>171.033</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>51.852</v>
+        <v>52.454</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>29.691</v>
+        <v>30.61</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>51.396</v>
+        <v>51.824</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>31.281</v>
+        <v>32.164</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>50.073</v>
+        <v>50.752</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>18.792</v>
+        <v>18.588</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>21.705</v>
+        <v>21.214</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.587</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="10">
@@ -2227,70 +2227,70 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>329.382</v>
+        <v>332.08</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>330.404</v>
+        <v>333.05</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>331.429</v>
+        <v>334.024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>133.272</v>
+        <v>137.629</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>124.605</v>
+        <v>128.962</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>131.142</v>
+        <v>134.57</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>107.393</v>
+        <v>108.912</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>224.036</v>
+        <v>225.112</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>107.393</v>
+        <v>108.912</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>171.157</v>
+        <v>175.509</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>256.356</v>
+        <v>259.435</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>169.503</v>
+        <v>173.122</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>260.679</v>
+        <v>263.85</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>164.498</v>
+        <v>168.799</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>51.138</v>
+        <v>51.644</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>29.082</v>
+        <v>29.808</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>50.686</v>
+        <v>51.016</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>30.747</v>
+        <v>31.441</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>49.243</v>
+        <v>49.818</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>18.496</v>
+        <v>18.377</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>21.604</v>
+        <v>21.208</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="11">
@@ -2298,70 +2298,70 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>331.429</v>
+        <v>334.024</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>332.276</v>
+        <v>334.828</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>333.126</v>
+        <v>335.634</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>131.142</v>
+        <v>134.57</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>122.142</v>
+        <v>125.57</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>129.069</v>
+        <v>131.596</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>108.169</v>
+        <v>109.44</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>224.957</v>
+        <v>226.195</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>108.169</v>
+        <v>109.44</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>169.996</v>
+        <v>173.454</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>255.977</v>
+        <v>258.712</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>168.403</v>
+        <v>171.157</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>260.391</v>
+        <v>263.198</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>163.154</v>
+        <v>166.568</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>50.483</v>
+        <v>50.88</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>28.5</v>
+        <v>29.037</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>50.035</v>
+        <v>50.252</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>30.241</v>
+        <v>30.75</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>48.472</v>
+        <v>48.927</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>18.231</v>
+        <v>18.177</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>21.535</v>
+        <v>21.215</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.549</v>
+        <v>0.5580000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2369,70 +2369,70 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>333.126</v>
+        <v>335.634</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>332.424</v>
+        <v>334.971</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>331.723</v>
+        <v>334.309</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>129.069</v>
+        <v>131.596</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>119.736</v>
+        <v>122.263</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>126.063</v>
+        <v>127.757</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>106.872</v>
+        <v>108.027</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>224.851</v>
+        <v>226.282</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>106.872</v>
+        <v>108.027</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>167.573</v>
+        <v>170.257</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>254.744</v>
+        <v>257.2</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>165.268</v>
+        <v>167.307</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>259.262</v>
+        <v>261.765</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>160.494</v>
+        <v>163.15</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>50.374</v>
+        <v>50.618</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>28.036</v>
+        <v>28.383</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>49.71</v>
+        <v>49.783</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>29.857</v>
+        <v>30.18</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>48.249</v>
+        <v>48.537</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>18.392</v>
+        <v>18.357</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>21.674</v>
+        <v>21.4</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.531</v>
+        <v>0.539</v>
       </c>
     </row>
     <row r="13">
@@ -2440,70 +2440,70 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>331.723</v>
+        <v>334.309</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>331.172</v>
+        <v>333.79</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>330.622</v>
+        <v>333.271</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>126.063</v>
+        <v>127.757</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>116.396</v>
+        <v>118.09</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>123.339</v>
+        <v>124.221</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>102.159</v>
+        <v>103.164</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>215.238</v>
+        <v>216.776</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>102.159</v>
+        <v>103.164</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>162.26</v>
+        <v>164.209</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>244.695</v>
+        <v>246.854</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>160.153</v>
+        <v>161.474</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>260.935</v>
+        <v>263.193</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>163.895</v>
+        <v>165.881</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>50.979</v>
+        <v>51.079</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>28.404</v>
+        <v>28.58</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>50.366</v>
+        <v>50.291</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>28.889</v>
+        <v>29.039</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>45.25</v>
+        <v>45.39</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>16.361</v>
+        <v>16.35</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>21.962</v>
+        <v>21.711</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.521</v>
+        <v>0.527</v>
       </c>
     </row>
     <row r="14">
@@ -2511,70 +2511,70 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>330.622</v>
+        <v>333.271</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>330.476</v>
+        <v>333.107</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>330.329</v>
+        <v>332.943</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>123.339</v>
+        <v>124.221</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>113.339</v>
+        <v>114.221</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>113.339</v>
+        <v>114.221</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>94.75700000000001</v>
+        <v>95.55</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>202.539</v>
+        <v>204.099</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>94.75700000000001</v>
+        <v>95.55</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>155.536</v>
+        <v>156.718</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>232.095</v>
+        <v>233.886</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>147.732</v>
+        <v>148.917</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>265.908</v>
+        <v>267.93</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>170.81</v>
+        <v>172.184</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>52.466</v>
+        <v>52.433</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>29.231</v>
+        <v>29.233</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>50.103</v>
+        <v>50.086</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>27.635</v>
+        <v>27.622</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>41.57</v>
+        <v>41.557</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>13.935</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>20.872</v>
+        <v>20.853</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>0.518</v>
+        <v>0.524</v>
       </c>
     </row>
   </sheetData>
@@ -2738,70 +2738,70 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>74.54900000000001</v>
+        <v>105.553</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>60.971</v>
+        <v>95.54300000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>63.755</v>
+        <v>93.875</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>128.809</v>
+        <v>132.448</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>218.617</v>
+        <v>217.162</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>128.809</v>
+        <v>132.448</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>148.826</v>
+        <v>169.363</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>226.96</v>
+        <v>237.25</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>143.723</v>
+        <v>162.342</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>230.978</v>
+        <v>241.455</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>142.51</v>
+        <v>163.312</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>30.06</v>
+        <v>38.553</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>15.584</v>
+        <v>23.748</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>26.333</v>
+        <v>35.328</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>18.83</v>
+        <v>25.922</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>25.33</v>
+        <v>35.805</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>6.501</v>
+        <v>9.882999999999999</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>10.75</v>
+        <v>11.58</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.712</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="3">
@@ -2809,70 +2809,70 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>86.122</v>
+        <v>109.11</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>74.42</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>80.163</v>
+        <v>101.847</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>124.726</v>
+        <v>127.875</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>222.7</v>
+        <v>221.735</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>124.726</v>
+        <v>127.875</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>151.57</v>
+        <v>168.098</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>234.805</v>
+        <v>242.975</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>148.266</v>
+        <v>163.477</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>238.772</v>
+        <v>247.126</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>145.241</v>
+        <v>161.934</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>34.625</v>
+        <v>40.472</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>18.478</v>
+        <v>24.135</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>32.73</v>
+        <v>38.536</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>21.142</v>
+        <v>26.201</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>30.823</v>
+        <v>37.845</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>9.680999999999999</v>
+        <v>11.644</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>14.251</v>
+        <v>14.4</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.699</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="4">
@@ -2880,70 +2880,70 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>95.55500000000001</v>
+        <v>113.62</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>84.849</v>
+        <v>104.084</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>90.995</v>
+        <v>107.719</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>120.894</v>
+        <v>123.731</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>226.531</v>
+        <v>225.878</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>120.894</v>
+        <v>123.731</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>154.098</v>
+        <v>167.985</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>241.901</v>
+        <v>248.706</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>151.312</v>
+        <v>164.052</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>245.86</v>
+        <v>252.845</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>147.698</v>
+        <v>161.688</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>38.323</v>
+        <v>42.561</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>20.534</v>
+        <v>24.74</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>36.968</v>
+        <v>41.042</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>22.871</v>
+        <v>26.703</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>35.063</v>
+        <v>40.071</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>12.192</v>
+        <v>13.368</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>16.434</v>
+        <v>16.302</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="5">
@@ -2951,70 +2951,70 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>101.646</v>
+        <v>116.392</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>91.36199999999999</v>
+        <v>106.901</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>97.803</v>
+        <v>111.256</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>120.3</v>
+        <v>122.774</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>227.125</v>
+        <v>226.836</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>120.3</v>
+        <v>122.774</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>157.493</v>
+        <v>169.176</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>244.812</v>
+        <v>250.764</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>155.041</v>
+        <v>165.685</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>248.833</v>
+        <v>254.954</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>151.06</v>
+        <v>162.792</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>40.196</v>
+        <v>43.471</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>21.913</v>
+        <v>25.233</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>39.111</v>
+        <v>42.183</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>24.11</v>
+        <v>27.163</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>37.215</v>
+        <v>41.046</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>13.105</v>
+        <v>13.884</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>17.198</v>
+        <v>16.949</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.658</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="6">
@@ -3022,70 +3022,70 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>105.617</v>
+        <v>117.867</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>95.483</v>
+        <v>108.31</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>102.218</v>
+        <v>113.234</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>119.774</v>
+        <v>121.935</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>227.651</v>
+        <v>227.675</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>119.774</v>
+        <v>121.935</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>159.69</v>
+        <v>169.59</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>246.864</v>
+        <v>252.125</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>157.462</v>
+        <v>166.403</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>250.958</v>
+        <v>256.376</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>153.176</v>
+        <v>163.093</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>41.406</v>
+        <v>44.028</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>22.754</v>
+        <v>25.441</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>40.478</v>
+        <v>42.881</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>24.889</v>
+        <v>27.371</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>38.561</v>
+        <v>41.613</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>13.673</v>
+        <v>14.243</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>17.724</v>
+        <v>17.44</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.633</v>
+        <v>0.652</v>
       </c>
     </row>
     <row r="7">
@@ -3093,70 +3093,70 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>108.18</v>
+        <v>118.413</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>98.047</v>
+        <v>108.716</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>105.084</v>
+        <v>114.137</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>119.298</v>
+        <v>121.183</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>228.128</v>
+        <v>228.427</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>119.298</v>
+        <v>121.183</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>161.043</v>
+        <v>169.431</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>248.305</v>
+        <v>252.978</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>158.98</v>
+        <v>166.471</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>252.478</v>
+        <v>257.295</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>154.419</v>
+        <v>162.802</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>42.202</v>
+        <v>44.338</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>23.257</v>
+        <v>25.451</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>41.375</v>
+        <v>43.285</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>25.371</v>
+        <v>27.401</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>39.416</v>
+        <v>41.896</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>14.045</v>
+        <v>14.495</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>18.118</v>
+        <v>17.834</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.611</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="8">
@@ -3164,70 +3164,70 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>109.77</v>
+        <v>118.286</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>99.54600000000001</v>
+        <v>108.401</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>106.896</v>
+        <v>114.28</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>118.86</v>
+        <v>120.5</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>228.565</v>
+        <v>229.11</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>118.86</v>
+        <v>120.5</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>161.793</v>
+        <v>168.854</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>249.302</v>
+        <v>253.461</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>159.858</v>
+        <v>166.072</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>253.558</v>
+        <v>257.843</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>155.039</v>
+        <v>162.083</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>42.723</v>
+        <v>44.469</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>23.534</v>
+        <v>25.321</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>41.966</v>
+        <v>43.482</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>25.653</v>
+        <v>27.307</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>39.946</v>
+        <v>41.974</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>14.293</v>
+        <v>14.668</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>18.432</v>
+        <v>18.162</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.59</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="9">
@@ -3235,70 +3235,70 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>110.664</v>
+        <v>117.666</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>100.29</v>
+        <v>107.556</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>107.961</v>
+        <v>113.871</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>118.455</v>
+        <v>119.873</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>228.971</v>
+        <v>229.737</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>118.455</v>
+        <v>119.873</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>162.105</v>
+        <v>167.973</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>249.971</v>
+        <v>253.668</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>160.272</v>
+        <v>165.337</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>254.311</v>
+        <v>258.117</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>155.208</v>
+        <v>161.052</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>43.052</v>
+        <v>44.468</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>23.654</v>
+        <v>25.088</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>42.346</v>
+        <v>43.529</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>25.795</v>
+        <v>27.121</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>40.253</v>
+        <v>41.9</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>14.458</v>
+        <v>14.78</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>18.693</v>
+        <v>18.442</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.571</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="10">
@@ -3306,70 +3306,70 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>111.048</v>
+        <v>116.679</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>100.482</v>
+        <v>106.319</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>108.482</v>
+        <v>113.056</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>118.077</v>
+        <v>119.296</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>229.349</v>
+        <v>230.314</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>118.077</v>
+        <v>119.296</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>162.092</v>
+        <v>166.87</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>250.395</v>
+        <v>253.67</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>160.345</v>
+        <v>164.356</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>254.819</v>
+        <v>258.184</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>155.045</v>
+        <v>159.797</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>43.243</v>
+        <v>44.365</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>23.659</v>
+        <v>24.779</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>42.575</v>
+        <v>43.462</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>25.836</v>
+        <v>26.867</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>40.398</v>
+        <v>41.708</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>14.562</v>
+        <v>14.841</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>18.916</v>
+        <v>18.683</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.553</v>
+        <v>0.5639999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -3377,70 +3377,70 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>111.051</v>
+        <v>115.416</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>100.263</v>
+        <v>104.784</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>108.596</v>
+        <v>111.934</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>117.723</v>
+        <v>118.761</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>229.703</v>
+        <v>230.849</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>117.723</v>
+        <v>118.761</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>161.836</v>
+        <v>165.605</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>250.632</v>
+        <v>253.517</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>160.161</v>
+        <v>163.197</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>255.139</v>
+        <v>258.093</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>154.633</v>
+        <v>158.379</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>43.33</v>
+        <v>44.182</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>23.581</v>
+        <v>24.414</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>42.691</v>
+        <v>43.305</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>25.802</v>
+        <v>26.563</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>40.421</v>
+        <v>41.422</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>14.619</v>
+        <v>14.859</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>19.11</v>
+        <v>18.891</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.537</v>
+        <v>0.546</v>
       </c>
     </row>
     <row r="12">
@@ -3448,70 +3448,70 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>347.426</v>
+        <v>349.61</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>346.078</v>
+        <v>348.335</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>344.731</v>
+        <v>347.061</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>106.427</v>
+        <v>109.932</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>97.32299999999999</v>
+        <v>100.8</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>107.203</v>
+        <v>109.442</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>117.39</v>
+        <v>118.265</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>229.581</v>
+        <v>230.914</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>115.602</v>
+        <v>116.575</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>158.452</v>
+        <v>161.468</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>249.358</v>
+        <v>251.957</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>157.659</v>
+        <v>159.898</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>253.463</v>
+        <v>256.136</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>151.8</v>
+        <v>154.752</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>42.196</v>
+        <v>42.909</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>22.973</v>
+        <v>23.582</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>42.841</v>
+        <v>43.192</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>24.828</v>
+        <v>25.417</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>39.876</v>
+        <v>40.644</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>15.048</v>
+        <v>15.228</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>19.868</v>
+        <v>19.61</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.519</v>
+        <v>0.526</v>
       </c>
     </row>
     <row r="13">
@@ -3519,70 +3519,70 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>344.731</v>
+        <v>347.061</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>343.67</v>
+        <v>346.059</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>342.609</v>
+        <v>345.058</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>107.244</v>
+        <v>109.539</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>97.437</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>107.21</v>
+        <v>108.381</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>111.245</v>
+        <v>112.04</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>219.354</v>
+        <v>220.815</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>109.891</v>
+        <v>110.763</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>154.521</v>
+        <v>156.69</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>240.022</v>
+        <v>242.283</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>153.525</v>
+        <v>154.967</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>256.937</v>
+        <v>259.294</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>157.951</v>
+        <v>160.088</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>43.951</v>
+        <v>44.353</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>23.951</v>
+        <v>24.302</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>44.293</v>
+        <v>44.377</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>24.67</v>
+        <v>24.989</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>38.089</v>
+        <v>38.524</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>13.419</v>
+        <v>13.535</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>20.342</v>
+        <v>20.076</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.512</v>
+        <v>0.519</v>
       </c>
     </row>
     <row r="14">
@@ -3590,70 +3590,70 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>342.609</v>
+        <v>345.058</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>342.326</v>
+        <v>344.741</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>342.043</v>
+        <v>344.424</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>108.931</v>
+        <v>110.018</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>97.86499999999999</v>
+        <v>99.036</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>98.265</v>
+        <v>99.483</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>102.214</v>
+        <v>102.907</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>206.049</v>
+        <v>207.55</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>101.874</v>
+        <v>102.525</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>149.377</v>
+        <v>150.645</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>228.109</v>
+        <v>229.968</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>141.542</v>
+        <v>142.857</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>263.923</v>
+        <v>265.972</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>167.776</v>
+        <v>169.202</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46.822</v>
+        <v>46.913</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>25.406</v>
+        <v>25.509</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>43.967</v>
+        <v>44.137</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>24.377</v>
+        <v>24.434</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>35.683</v>
+        <v>35.825</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>11.307</v>
+        <v>11.391</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>18.561</v>
+        <v>18.628</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>0.514</v>
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>

--- a/export/Приложение_Б.xlsx
+++ b/export/Приложение_Б.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Втулочное" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Среднее" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Периферийное" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Втулочное" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Среднее" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Периферийное" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/export/Приложение_Б.xlsx
+++ b/export/Приложение_Б.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Втулочное" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Среднее" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Периферийное" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Втулочное" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Среднее" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Периферийное" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
